--- a/Proyecto/docs/Pruebas de Caja Negra_Blanca/Pruebas de Caja Blanca-SistemaPOS.xlsx
+++ b/Proyecto/docs/Pruebas de Caja Negra_Blanca/Pruebas de Caja Blanca-SistemaPOS.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29929"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="24334"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/01f32f4e8c9e178e/Desktop/Analisis y Diseño/36289_AnalisisYDisenoDeSistemas/Proyecto/docs/Pruebas de Caja Negra_Blanca/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="260" documentId="11_94B3DA253D63A0DE445D4A83045116E5BA157345" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{7AA1E961-23A3-4E9A-93F6-020A138D855D}"/>
+  <xr:revisionPtr revIDLastSave="263" documentId="11_94B3DA253D63A0DE445D4A83045116E5BA157345" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{97E470D3-C7FC-4742-A0A7-1ADB363A31FB}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11040" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Usuario - Administrador" sheetId="1" r:id="rId1"/>
@@ -28,16 +28,17 @@
         <xcalcf:feature name="microsoft.com:FV"/>
         <xcalcf:feature name="microsoft.com:CNMTM"/>
         <xcalcf:feature name="microsoft.com:LET_WF"/>
-        <xcalcf:feature name="microsoft.com:LAMBDA_WF"/>
-        <xcalcf:feature name="microsoft.com:ARRAYTEXT_WF"/>
       </xcalcf:calcFeatures>
+    </ext>
+    <ext xmlns:xlwcv="http://schemas.microsoft.com/office/spreadsheetml/2024/workbookCompatibilityVersion" uri="{D14903EA-33C4-47F7-8F05-3474C54BE107}">
+      <xlwcv:version setVersion="1"/>
     </ext>
   </extLst>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="341" uniqueCount="135">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="341" uniqueCount="136">
   <si>
     <t>USUARIO - Administrador</t>
   </si>
@@ -1026,6 +1027,9 @@
   </si>
   <si>
     <t>La venta existe y ya está pagada</t>
+  </si>
+  <si>
+    <t>CLIENTE</t>
   </si>
 </sst>
 </file>
@@ -1351,7 +1355,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="75">
+  <cellXfs count="73">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
     <xf numFmtId="0" fontId="3" fillId="2" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -1468,59 +1472,55 @@
     <xf numFmtId="0" fontId="19" fillId="6" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1" indent="1"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="8" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="8" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="9" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="18" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="3" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="2" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="17" fillId="3" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="21" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="5" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="2" fillId="3" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="3" fillId="2" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="17" fillId="3" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="5" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="2" fillId="3" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="2" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="8" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="8" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="9" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="18" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -1752,11 +1752,11 @@
   </cols>
   <sheetData>
     <row r="2" spans="2:4">
-      <c r="B2" s="64" t="s">
+      <c r="B2" s="67" t="s">
         <v>0</v>
       </c>
-      <c r="C2" s="65"/>
-      <c r="D2" s="65"/>
+      <c r="C2" s="68"/>
+      <c r="D2" s="68"/>
     </row>
     <row r="3" spans="2:4" ht="12.75">
       <c r="B3" s="1"/>
@@ -1764,25 +1764,25 @@
       <c r="D3" s="1"/>
     </row>
     <row r="4" spans="2:4" ht="12.75">
-      <c r="B4" s="48" t="s">
+      <c r="B4" s="56" t="s">
         <v>1</v>
       </c>
-      <c r="C4" s="49"/>
-      <c r="D4" s="50"/>
+      <c r="C4" s="57"/>
+      <c r="D4" s="58"/>
     </row>
     <row r="5" spans="2:4" ht="12.75">
-      <c r="B5" s="48" t="s">
-        <v>2</v>
-      </c>
-      <c r="C5" s="49"/>
-      <c r="D5" s="50"/>
+      <c r="B5" s="56" t="s">
+        <v>2</v>
+      </c>
+      <c r="C5" s="57"/>
+      <c r="D5" s="58"/>
     </row>
     <row r="6" spans="2:4" ht="192" customHeight="1">
-      <c r="B6" s="66" t="s">
+      <c r="B6" s="59" t="s">
         <v>3</v>
       </c>
-      <c r="C6" s="49"/>
-      <c r="D6" s="50"/>
+      <c r="C6" s="57"/>
+      <c r="D6" s="58"/>
     </row>
     <row r="7" spans="2:4" ht="12.75">
       <c r="B7" s="2" t="s">
@@ -1840,25 +1840,25 @@
       </c>
     </row>
     <row r="15" spans="2:4" ht="12.75">
-      <c r="B15" s="61" t="s">
+      <c r="B15" s="60" t="s">
         <v>13</v>
       </c>
-      <c r="C15" s="49"/>
-      <c r="D15" s="50"/>
+      <c r="C15" s="57"/>
+      <c r="D15" s="58"/>
     </row>
     <row r="16" spans="2:4" ht="22.5" customHeight="1">
-      <c r="B16" s="61" t="s">
-        <v>2</v>
-      </c>
-      <c r="C16" s="49"/>
-      <c r="D16" s="50"/>
+      <c r="B16" s="60" t="s">
+        <v>2</v>
+      </c>
+      <c r="C16" s="57"/>
+      <c r="D16" s="58"/>
     </row>
     <row r="17" spans="2:4" ht="177" customHeight="1">
-      <c r="B17" s="62" t="s">
+      <c r="B17" s="61" t="s">
         <v>14</v>
       </c>
-      <c r="C17" s="49"/>
-      <c r="D17" s="50"/>
+      <c r="C17" s="57"/>
+      <c r="D17" s="58"/>
     </row>
     <row r="18" spans="2:4" ht="14.25" customHeight="1">
       <c r="B18" s="8" t="s">
@@ -1905,25 +1905,25 @@
       </c>
     </row>
     <row r="25" spans="2:4" ht="12.75">
-      <c r="B25" s="61" t="s">
+      <c r="B25" s="60" t="s">
         <v>18</v>
       </c>
-      <c r="C25" s="49"/>
-      <c r="D25" s="50"/>
+      <c r="C25" s="57"/>
+      <c r="D25" s="58"/>
     </row>
     <row r="26" spans="2:4" ht="12.75">
-      <c r="B26" s="61" t="s">
-        <v>2</v>
-      </c>
-      <c r="C26" s="49"/>
-      <c r="D26" s="50"/>
+      <c r="B26" s="60" t="s">
+        <v>2</v>
+      </c>
+      <c r="C26" s="57"/>
+      <c r="D26" s="58"/>
     </row>
     <row r="27" spans="2:4" ht="197.25" customHeight="1">
-      <c r="B27" s="62" t="s">
+      <c r="B27" s="61" t="s">
         <v>19</v>
       </c>
-      <c r="C27" s="49"/>
-      <c r="D27" s="50"/>
+      <c r="C27" s="57"/>
+      <c r="D27" s="58"/>
     </row>
     <row r="28" spans="2:4" ht="12.75">
       <c r="B28" s="10" t="s">
@@ -1981,25 +1981,25 @@
       </c>
     </row>
     <row r="34" spans="2:4" ht="12.75">
-      <c r="B34" s="61" t="s">
+      <c r="B34" s="60" t="s">
         <v>24</v>
       </c>
-      <c r="C34" s="49"/>
-      <c r="D34" s="50"/>
+      <c r="C34" s="57"/>
+      <c r="D34" s="58"/>
     </row>
     <row r="35" spans="2:4" ht="12.75">
-      <c r="B35" s="61" t="s">
-        <v>2</v>
-      </c>
-      <c r="C35" s="49"/>
-      <c r="D35" s="50"/>
+      <c r="B35" s="60" t="s">
+        <v>2</v>
+      </c>
+      <c r="C35" s="57"/>
+      <c r="D35" s="58"/>
     </row>
     <row r="36" spans="2:4" ht="12.75">
-      <c r="B36" s="63" t="s">
+      <c r="B36" s="62" t="s">
         <v>25</v>
       </c>
-      <c r="C36" s="49"/>
-      <c r="D36" s="50"/>
+      <c r="C36" s="57"/>
+      <c r="D36" s="58"/>
     </row>
     <row r="37" spans="2:4" ht="12.75">
       <c r="B37" s="10" t="s">
@@ -2046,25 +2046,25 @@
       </c>
     </row>
     <row r="43" spans="2:4" ht="12.75">
-      <c r="B43" s="61" t="s">
+      <c r="B43" s="60" t="s">
         <v>28</v>
       </c>
-      <c r="C43" s="49"/>
-      <c r="D43" s="50"/>
+      <c r="C43" s="57"/>
+      <c r="D43" s="58"/>
     </row>
     <row r="44" spans="2:4" ht="12.75">
-      <c r="B44" s="61" t="s">
-        <v>2</v>
-      </c>
-      <c r="C44" s="49"/>
-      <c r="D44" s="50"/>
+      <c r="B44" s="60" t="s">
+        <v>2</v>
+      </c>
+      <c r="C44" s="57"/>
+      <c r="D44" s="58"/>
     </row>
     <row r="45" spans="2:4" ht="150" customHeight="1">
-      <c r="B45" s="62" t="s">
+      <c r="B45" s="61" t="s">
         <v>29</v>
       </c>
-      <c r="C45" s="49"/>
-      <c r="D45" s="50"/>
+      <c r="C45" s="57"/>
+      <c r="D45" s="58"/>
     </row>
     <row r="46" spans="2:4" ht="12.75">
       <c r="B46" s="10" t="s">
@@ -2111,25 +2111,25 @@
       </c>
     </row>
     <row r="52" spans="2:4" ht="12.75">
-      <c r="B52" s="61" t="s">
+      <c r="B52" s="60" t="s">
         <v>33</v>
       </c>
-      <c r="C52" s="49"/>
-      <c r="D52" s="50"/>
+      <c r="C52" s="57"/>
+      <c r="D52" s="58"/>
     </row>
     <row r="53" spans="2:4" ht="12.75">
-      <c r="B53" s="61" t="s">
-        <v>2</v>
-      </c>
-      <c r="C53" s="49"/>
-      <c r="D53" s="50"/>
+      <c r="B53" s="60" t="s">
+        <v>2</v>
+      </c>
+      <c r="C53" s="57"/>
+      <c r="D53" s="58"/>
     </row>
     <row r="54" spans="2:4" ht="99" customHeight="1">
-      <c r="B54" s="62" t="s">
+      <c r="B54" s="61" t="s">
         <v>34</v>
       </c>
-      <c r="C54" s="49"/>
-      <c r="D54" s="50"/>
+      <c r="C54" s="57"/>
+      <c r="D54" s="58"/>
     </row>
     <row r="55" spans="2:4" ht="12.75">
       <c r="B55" s="19" t="s">
@@ -2176,25 +2176,25 @@
       </c>
     </row>
     <row r="61" spans="2:4" ht="12.75">
-      <c r="B61" s="61" t="s">
+      <c r="B61" s="60" t="s">
         <v>37</v>
       </c>
-      <c r="C61" s="49"/>
-      <c r="D61" s="50"/>
+      <c r="C61" s="57"/>
+      <c r="D61" s="58"/>
     </row>
     <row r="62" spans="2:4" ht="12.75">
-      <c r="B62" s="61" t="s">
-        <v>2</v>
-      </c>
-      <c r="C62" s="49"/>
-      <c r="D62" s="50"/>
+      <c r="B62" s="60" t="s">
+        <v>2</v>
+      </c>
+      <c r="C62" s="57"/>
+      <c r="D62" s="58"/>
     </row>
     <row r="63" spans="2:4" ht="227.25" customHeight="1">
-      <c r="B63" s="62" t="s">
+      <c r="B63" s="61" t="s">
         <v>38</v>
       </c>
-      <c r="C63" s="49"/>
-      <c r="D63" s="50"/>
+      <c r="C63" s="57"/>
+      <c r="D63" s="58"/>
     </row>
     <row r="64" spans="2:4" ht="12.75">
       <c r="B64" s="23" t="s">
@@ -2252,25 +2252,25 @@
       </c>
     </row>
     <row r="71" spans="2:4" ht="12.75">
-      <c r="B71" s="61" t="s">
+      <c r="B71" s="60" t="s">
         <v>43</v>
       </c>
-      <c r="C71" s="49"/>
-      <c r="D71" s="50"/>
+      <c r="C71" s="57"/>
+      <c r="D71" s="58"/>
     </row>
     <row r="72" spans="2:4" ht="12.75">
-      <c r="B72" s="61" t="s">
-        <v>2</v>
-      </c>
-      <c r="C72" s="49"/>
-      <c r="D72" s="50"/>
+      <c r="B72" s="60" t="s">
+        <v>2</v>
+      </c>
+      <c r="C72" s="57"/>
+      <c r="D72" s="58"/>
     </row>
     <row r="73" spans="2:4" ht="96" customHeight="1">
-      <c r="B73" s="62" t="s">
+      <c r="B73" s="61" t="s">
         <v>44</v>
       </c>
-      <c r="C73" s="49"/>
-      <c r="D73" s="50"/>
+      <c r="C73" s="57"/>
+      <c r="D73" s="58"/>
     </row>
     <row r="74" spans="2:4" ht="12.75">
       <c r="B74" s="26" t="s">
@@ -2318,21 +2318,6 @@
     </row>
   </sheetData>
   <mergeCells count="25">
-    <mergeCell ref="B2:D2"/>
-    <mergeCell ref="B4:D4"/>
-    <mergeCell ref="B5:D5"/>
-    <mergeCell ref="B6:D6"/>
-    <mergeCell ref="B15:D15"/>
-    <mergeCell ref="B16:D16"/>
-    <mergeCell ref="B17:D17"/>
-    <mergeCell ref="B25:D25"/>
-    <mergeCell ref="B26:D26"/>
-    <mergeCell ref="B27:D27"/>
-    <mergeCell ref="B34:D34"/>
-    <mergeCell ref="B35:D35"/>
-    <mergeCell ref="B36:D36"/>
-    <mergeCell ref="B43:D43"/>
-    <mergeCell ref="B63:D63"/>
     <mergeCell ref="B71:D71"/>
     <mergeCell ref="B72:D72"/>
     <mergeCell ref="B73:D73"/>
@@ -2343,6 +2328,21 @@
     <mergeCell ref="B54:D54"/>
     <mergeCell ref="B61:D61"/>
     <mergeCell ref="B62:D62"/>
+    <mergeCell ref="B34:D34"/>
+    <mergeCell ref="B35:D35"/>
+    <mergeCell ref="B36:D36"/>
+    <mergeCell ref="B43:D43"/>
+    <mergeCell ref="B63:D63"/>
+    <mergeCell ref="B16:D16"/>
+    <mergeCell ref="B17:D17"/>
+    <mergeCell ref="B25:D25"/>
+    <mergeCell ref="B26:D26"/>
+    <mergeCell ref="B27:D27"/>
+    <mergeCell ref="B2:D2"/>
+    <mergeCell ref="B4:D4"/>
+    <mergeCell ref="B5:D5"/>
+    <mergeCell ref="B6:D6"/>
+    <mergeCell ref="B15:D15"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
@@ -2363,11 +2363,11 @@
   </cols>
   <sheetData>
     <row r="2" spans="2:4">
-      <c r="B2" s="64" t="s">
+      <c r="B2" s="67" t="s">
         <v>47</v>
       </c>
-      <c r="C2" s="65"/>
-      <c r="D2" s="65"/>
+      <c r="C2" s="68"/>
+      <c r="D2" s="68"/>
     </row>
     <row r="3" spans="2:4" ht="12.75">
       <c r="B3" s="1"/>
@@ -2375,25 +2375,25 @@
       <c r="D3" s="1"/>
     </row>
     <row r="4" spans="2:4" ht="12.75">
-      <c r="B4" s="48" t="s">
+      <c r="B4" s="56" t="s">
         <v>1</v>
       </c>
-      <c r="C4" s="49"/>
-      <c r="D4" s="50"/>
+      <c r="C4" s="57"/>
+      <c r="D4" s="58"/>
     </row>
     <row r="5" spans="2:4" ht="12.75">
-      <c r="B5" s="48" t="s">
-        <v>2</v>
-      </c>
-      <c r="C5" s="49"/>
-      <c r="D5" s="50"/>
+      <c r="B5" s="56" t="s">
+        <v>2</v>
+      </c>
+      <c r="C5" s="57"/>
+      <c r="D5" s="58"/>
     </row>
     <row r="6" spans="2:4" ht="184.5" customHeight="1">
-      <c r="B6" s="66" t="s">
+      <c r="B6" s="59" t="s">
         <v>3</v>
       </c>
-      <c r="C6" s="49"/>
-      <c r="D6" s="50"/>
+      <c r="C6" s="57"/>
+      <c r="D6" s="58"/>
     </row>
     <row r="7" spans="2:4" ht="12.75">
       <c r="B7" s="2" t="s">
@@ -2451,25 +2451,25 @@
       </c>
     </row>
     <row r="15" spans="2:4" ht="12.75">
-      <c r="B15" s="48" t="s">
+      <c r="B15" s="56" t="s">
         <v>48</v>
       </c>
-      <c r="C15" s="49"/>
-      <c r="D15" s="50"/>
+      <c r="C15" s="57"/>
+      <c r="D15" s="58"/>
     </row>
     <row r="16" spans="2:4" ht="12.75">
-      <c r="B16" s="48" t="s">
-        <v>2</v>
-      </c>
-      <c r="C16" s="49"/>
-      <c r="D16" s="50"/>
+      <c r="B16" s="56" t="s">
+        <v>2</v>
+      </c>
+      <c r="C16" s="57"/>
+      <c r="D16" s="58"/>
     </row>
     <row r="17" spans="2:4" ht="222.75" customHeight="1">
-      <c r="B17" s="66" t="s">
+      <c r="B17" s="59" t="s">
         <v>49</v>
       </c>
-      <c r="C17" s="49"/>
-      <c r="D17" s="50"/>
+      <c r="C17" s="57"/>
+      <c r="D17" s="58"/>
     </row>
     <row r="18" spans="2:4" ht="12.75">
       <c r="B18" s="26" t="s">
@@ -2527,25 +2527,25 @@
       </c>
     </row>
     <row r="26" spans="2:4" ht="12.75">
-      <c r="B26" s="48" t="s">
+      <c r="B26" s="56" t="s">
         <v>54</v>
       </c>
-      <c r="C26" s="49"/>
-      <c r="D26" s="50"/>
+      <c r="C26" s="57"/>
+      <c r="D26" s="58"/>
     </row>
     <row r="27" spans="2:4" ht="12.75">
-      <c r="B27" s="48" t="s">
-        <v>2</v>
-      </c>
-      <c r="C27" s="49"/>
-      <c r="D27" s="50"/>
+      <c r="B27" s="56" t="s">
+        <v>2</v>
+      </c>
+      <c r="C27" s="57"/>
+      <c r="D27" s="58"/>
     </row>
     <row r="28" spans="2:4" ht="138" customHeight="1">
-      <c r="B28" s="66" t="s">
+      <c r="B28" s="59" t="s">
         <v>55</v>
       </c>
-      <c r="C28" s="49"/>
-      <c r="D28" s="50"/>
+      <c r="C28" s="57"/>
+      <c r="D28" s="58"/>
     </row>
     <row r="29" spans="2:4" ht="12.75">
       <c r="B29" s="26" t="s">
@@ -2597,25 +2597,25 @@
       <c r="D33" s="32"/>
     </row>
     <row r="36" spans="2:4" ht="12.75">
-      <c r="B36" s="48" t="s">
+      <c r="B36" s="56" t="s">
         <v>59</v>
       </c>
-      <c r="C36" s="49"/>
-      <c r="D36" s="50"/>
+      <c r="C36" s="57"/>
+      <c r="D36" s="58"/>
     </row>
     <row r="37" spans="2:4" ht="16.5" customHeight="1">
-      <c r="B37" s="48" t="s">
-        <v>2</v>
-      </c>
-      <c r="C37" s="49"/>
-      <c r="D37" s="50"/>
+      <c r="B37" s="56" t="s">
+        <v>2</v>
+      </c>
+      <c r="C37" s="57"/>
+      <c r="D37" s="58"/>
     </row>
     <row r="38" spans="2:4" ht="212.25" customHeight="1">
-      <c r="B38" s="66" t="s">
+      <c r="B38" s="59" t="s">
         <v>60</v>
       </c>
-      <c r="C38" s="49"/>
-      <c r="D38" s="50"/>
+      <c r="C38" s="57"/>
+      <c r="D38" s="58"/>
     </row>
     <row r="39" spans="2:4" ht="12.75">
       <c r="B39" s="26" t="s">
@@ -2662,25 +2662,25 @@
       </c>
     </row>
     <row r="46" spans="2:4" ht="12.75">
-      <c r="B46" s="48" t="s">
+      <c r="B46" s="56" t="s">
         <v>64</v>
       </c>
-      <c r="C46" s="49"/>
-      <c r="D46" s="50"/>
+      <c r="C46" s="57"/>
+      <c r="D46" s="58"/>
     </row>
     <row r="47" spans="2:4" ht="12.75">
-      <c r="B47" s="48" t="s">
-        <v>2</v>
-      </c>
-      <c r="C47" s="49"/>
-      <c r="D47" s="50"/>
+      <c r="B47" s="56" t="s">
+        <v>2</v>
+      </c>
+      <c r="C47" s="57"/>
+      <c r="D47" s="58"/>
     </row>
     <row r="48" spans="2:4" ht="139.5" customHeight="1">
-      <c r="B48" s="66" t="s">
+      <c r="B48" s="59" t="s">
         <v>65</v>
       </c>
-      <c r="C48" s="49"/>
-      <c r="D48" s="50"/>
+      <c r="C48" s="57"/>
+      <c r="D48" s="58"/>
     </row>
     <row r="49" spans="2:4" ht="12.75">
       <c r="B49" s="26" t="s">
@@ -2727,25 +2727,25 @@
       </c>
     </row>
     <row r="56" spans="2:4" ht="12.75">
-      <c r="B56" s="48" t="s">
+      <c r="B56" s="56" t="s">
         <v>69</v>
       </c>
-      <c r="C56" s="49"/>
-      <c r="D56" s="50"/>
+      <c r="C56" s="57"/>
+      <c r="D56" s="58"/>
     </row>
     <row r="57" spans="2:4" ht="12.75">
-      <c r="B57" s="48" t="s">
-        <v>2</v>
-      </c>
-      <c r="C57" s="49"/>
-      <c r="D57" s="50"/>
+      <c r="B57" s="56" t="s">
+        <v>2</v>
+      </c>
+      <c r="C57" s="57"/>
+      <c r="D57" s="58"/>
     </row>
     <row r="58" spans="2:4" ht="193.5" customHeight="1">
-      <c r="B58" s="66" t="s">
+      <c r="B58" s="59" t="s">
         <v>70</v>
       </c>
-      <c r="C58" s="49"/>
-      <c r="D58" s="50"/>
+      <c r="C58" s="57"/>
+      <c r="D58" s="58"/>
     </row>
     <row r="59" spans="2:4" ht="12.75">
       <c r="B59" s="26" t="s">
@@ -2793,16 +2793,6 @@
     </row>
   </sheetData>
   <mergeCells count="19">
-    <mergeCell ref="B2:D2"/>
-    <mergeCell ref="B4:D4"/>
-    <mergeCell ref="B5:D5"/>
-    <mergeCell ref="B6:D6"/>
-    <mergeCell ref="B15:D15"/>
-    <mergeCell ref="B16:D16"/>
-    <mergeCell ref="B17:D17"/>
-    <mergeCell ref="B47:D47"/>
-    <mergeCell ref="B48:D48"/>
-    <mergeCell ref="B56:D56"/>
     <mergeCell ref="B57:D57"/>
     <mergeCell ref="B58:D58"/>
     <mergeCell ref="B26:D26"/>
@@ -2812,6 +2802,16 @@
     <mergeCell ref="B37:D37"/>
     <mergeCell ref="B38:D38"/>
     <mergeCell ref="B46:D46"/>
+    <mergeCell ref="B16:D16"/>
+    <mergeCell ref="B17:D17"/>
+    <mergeCell ref="B47:D47"/>
+    <mergeCell ref="B48:D48"/>
+    <mergeCell ref="B56:D56"/>
+    <mergeCell ref="B2:D2"/>
+    <mergeCell ref="B4:D4"/>
+    <mergeCell ref="B5:D5"/>
+    <mergeCell ref="B6:D6"/>
+    <mergeCell ref="B15:D15"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
@@ -2828,11 +2828,11 @@
   </cols>
   <sheetData>
     <row r="3" spans="2:4" ht="15.75">
-      <c r="B3" s="58" t="s">
-        <v>94</v>
-      </c>
-      <c r="C3" s="59"/>
-      <c r="D3" s="59"/>
+      <c r="B3" s="67" t="s">
+        <v>135</v>
+      </c>
+      <c r="C3" s="68"/>
+      <c r="D3" s="68"/>
     </row>
     <row r="4" spans="2:4">
       <c r="B4" s="1"/>
@@ -2840,25 +2840,25 @@
       <c r="D4" s="1"/>
     </row>
     <row r="5" spans="2:4">
-      <c r="B5" s="48" t="s">
+      <c r="B5" s="56" t="s">
         <v>111</v>
       </c>
-      <c r="C5" s="49"/>
-      <c r="D5" s="50"/>
+      <c r="C5" s="57"/>
+      <c r="D5" s="58"/>
     </row>
     <row r="6" spans="2:4" ht="15.75" customHeight="1">
-      <c r="B6" s="48" t="s">
-        <v>2</v>
-      </c>
-      <c r="C6" s="49"/>
-      <c r="D6" s="50"/>
+      <c r="B6" s="56" t="s">
+        <v>2</v>
+      </c>
+      <c r="C6" s="57"/>
+      <c r="D6" s="58"/>
     </row>
     <row r="7" spans="2:4" ht="288.75" customHeight="1">
-      <c r="B7" s="60" t="s">
+      <c r="B7" s="69" t="s">
         <v>112</v>
       </c>
-      <c r="C7" s="52"/>
-      <c r="D7" s="53"/>
+      <c r="C7" s="64"/>
+      <c r="D7" s="65"/>
     </row>
     <row r="8" spans="2:4">
       <c r="B8" s="43" t="s">
@@ -2875,7 +2875,7 @@
       <c r="B9" s="38">
         <v>1</v>
       </c>
-      <c r="C9" s="67" t="s">
+      <c r="C9" s="48" t="s">
         <v>113</v>
       </c>
       <c r="D9" s="40" t="s">
@@ -2886,7 +2886,7 @@
       <c r="B10" s="38">
         <v>2</v>
       </c>
-      <c r="C10" s="68" t="s">
+      <c r="C10" s="49" t="s">
         <v>114</v>
       </c>
       <c r="D10" s="40" t="s">
@@ -2908,7 +2908,7 @@
       <c r="B12" s="38">
         <v>4</v>
       </c>
-      <c r="C12" s="69" t="s">
+      <c r="C12" s="50" t="s">
         <v>116</v>
       </c>
       <c r="D12" s="42" t="s">
@@ -2916,25 +2916,25 @@
       </c>
     </row>
     <row r="16" spans="2:4">
-      <c r="B16" s="54" t="s">
+      <c r="B16" s="66" t="s">
         <v>121</v>
       </c>
-      <c r="C16" s="49"/>
-      <c r="D16" s="50"/>
+      <c r="C16" s="57"/>
+      <c r="D16" s="58"/>
     </row>
     <row r="17" spans="2:4" ht="18.75" customHeight="1">
-      <c r="B17" s="48" t="s">
-        <v>2</v>
-      </c>
-      <c r="C17" s="49"/>
-      <c r="D17" s="50"/>
+      <c r="B17" s="56" t="s">
+        <v>2</v>
+      </c>
+      <c r="C17" s="57"/>
+      <c r="D17" s="58"/>
     </row>
     <row r="18" spans="2:4" ht="132" customHeight="1">
-      <c r="B18" s="51" t="s">
+      <c r="B18" s="63" t="s">
         <v>117</v>
       </c>
-      <c r="C18" s="52"/>
-      <c r="D18" s="53"/>
+      <c r="C18" s="64"/>
+      <c r="D18" s="65"/>
     </row>
     <row r="19" spans="2:4">
       <c r="B19" s="43" t="s">
@@ -2951,7 +2951,7 @@
       <c r="B20" s="38">
         <v>1</v>
       </c>
-      <c r="C20" s="73" t="s">
+      <c r="C20" s="54" t="s">
         <v>118</v>
       </c>
       <c r="D20" s="40" t="s">
@@ -2962,7 +2962,7 @@
       <c r="B21" s="38">
         <v>2</v>
       </c>
-      <c r="C21" s="73" t="s">
+      <c r="C21" s="54" t="s">
         <v>119</v>
       </c>
       <c r="D21" s="40" t="s">
@@ -2973,7 +2973,7 @@
       <c r="B22" s="38">
         <v>3</v>
       </c>
-      <c r="C22" s="73" t="s">
+      <c r="C22" s="54" t="s">
         <v>120</v>
       </c>
       <c r="D22" s="42" t="s">
@@ -2981,30 +2981,30 @@
       </c>
     </row>
     <row r="23" spans="2:4">
-      <c r="B23" s="70"/>
-      <c r="C23" s="71"/>
-      <c r="D23" s="72"/>
+      <c r="B23" s="51"/>
+      <c r="C23" s="52"/>
+      <c r="D23" s="53"/>
     </row>
     <row r="25" spans="2:4">
-      <c r="B25" s="54" t="s">
+      <c r="B25" s="66" t="s">
         <v>126</v>
       </c>
-      <c r="C25" s="49"/>
-      <c r="D25" s="50"/>
+      <c r="C25" s="57"/>
+      <c r="D25" s="58"/>
     </row>
     <row r="26" spans="2:4" ht="13.5" customHeight="1">
-      <c r="B26" s="48" t="s">
-        <v>2</v>
-      </c>
-      <c r="C26" s="49"/>
-      <c r="D26" s="50"/>
+      <c r="B26" s="56" t="s">
+        <v>2</v>
+      </c>
+      <c r="C26" s="57"/>
+      <c r="D26" s="58"/>
     </row>
     <row r="27" spans="2:4" ht="168" customHeight="1">
-      <c r="B27" s="51" t="s">
+      <c r="B27" s="63" t="s">
         <v>125</v>
       </c>
-      <c r="C27" s="52"/>
-      <c r="D27" s="53"/>
+      <c r="C27" s="64"/>
+      <c r="D27" s="65"/>
     </row>
     <row r="28" spans="2:4">
       <c r="B28" s="43" t="s">
@@ -3021,7 +3021,7 @@
       <c r="B29" s="38">
         <v>1</v>
       </c>
-      <c r="C29" s="73" t="s">
+      <c r="C29" s="54" t="s">
         <v>122</v>
       </c>
       <c r="D29" s="40" t="s">
@@ -3032,7 +3032,7 @@
       <c r="B30" s="38">
         <v>2</v>
       </c>
-      <c r="C30" s="73" t="s">
+      <c r="C30" s="54" t="s">
         <v>123</v>
       </c>
       <c r="D30" s="40" t="s">
@@ -3043,7 +3043,7 @@
       <c r="B31" s="38">
         <v>3</v>
       </c>
-      <c r="C31" s="73" t="s">
+      <c r="C31" s="54" t="s">
         <v>124</v>
       </c>
       <c r="D31" s="42" t="s">
@@ -3051,25 +3051,25 @@
       </c>
     </row>
     <row r="34" spans="2:4">
-      <c r="B34" s="54" t="s">
+      <c r="B34" s="66" t="s">
         <v>130</v>
       </c>
-      <c r="C34" s="49"/>
-      <c r="D34" s="50"/>
+      <c r="C34" s="57"/>
+      <c r="D34" s="58"/>
     </row>
     <row r="35" spans="2:4">
-      <c r="B35" s="48" t="s">
-        <v>2</v>
-      </c>
-      <c r="C35" s="49"/>
-      <c r="D35" s="50"/>
+      <c r="B35" s="56" t="s">
+        <v>2</v>
+      </c>
+      <c r="C35" s="57"/>
+      <c r="D35" s="58"/>
     </row>
     <row r="36" spans="2:4" ht="185.25" customHeight="1">
-      <c r="B36" s="51" t="s">
+      <c r="B36" s="63" t="s">
         <v>127</v>
       </c>
-      <c r="C36" s="52"/>
-      <c r="D36" s="53"/>
+      <c r="C36" s="64"/>
+      <c r="D36" s="65"/>
     </row>
     <row r="37" spans="2:4">
       <c r="B37" s="43" t="s">
@@ -3086,7 +3086,7 @@
       <c r="B38" s="38">
         <v>1</v>
       </c>
-      <c r="C38" s="73" t="s">
+      <c r="C38" s="54" t="s">
         <v>107</v>
       </c>
       <c r="D38" s="40" t="s">
@@ -3097,7 +3097,7 @@
       <c r="B39" s="38">
         <v>2</v>
       </c>
-      <c r="C39" s="73" t="s">
+      <c r="C39" s="54" t="s">
         <v>128</v>
       </c>
       <c r="D39" s="40" t="s">
@@ -3108,7 +3108,7 @@
       <c r="B40" s="38">
         <v>3</v>
       </c>
-      <c r="C40" s="73" t="s">
+      <c r="C40" s="54" t="s">
         <v>129</v>
       </c>
       <c r="D40" s="42" t="s">
@@ -3116,25 +3116,25 @@
       </c>
     </row>
     <row r="43" spans="2:4">
-      <c r="B43" s="54" t="s">
+      <c r="B43" s="66" t="s">
         <v>111</v>
       </c>
-      <c r="C43" s="49"/>
-      <c r="D43" s="50"/>
+      <c r="C43" s="57"/>
+      <c r="D43" s="58"/>
     </row>
     <row r="44" spans="2:4">
-      <c r="B44" s="48" t="s">
-        <v>2</v>
-      </c>
-      <c r="C44" s="49"/>
-      <c r="D44" s="50"/>
+      <c r="B44" s="56" t="s">
+        <v>2</v>
+      </c>
+      <c r="C44" s="57"/>
+      <c r="D44" s="58"/>
     </row>
     <row r="45" spans="2:4" ht="222.75" customHeight="1">
-      <c r="B45" s="51" t="s">
+      <c r="B45" s="63" t="s">
         <v>131</v>
       </c>
-      <c r="C45" s="52"/>
-      <c r="D45" s="53"/>
+      <c r="C45" s="64"/>
+      <c r="D45" s="65"/>
     </row>
     <row r="46" spans="2:4">
       <c r="B46" s="43" t="s">
@@ -3151,7 +3151,7 @@
       <c r="B47" s="38">
         <v>1</v>
       </c>
-      <c r="C47" s="73" t="s">
+      <c r="C47" s="54" t="s">
         <v>107</v>
       </c>
       <c r="D47" s="40" t="s">
@@ -3162,7 +3162,7 @@
       <c r="B48" s="38">
         <v>2</v>
       </c>
-      <c r="C48" s="73" t="s">
+      <c r="C48" s="54" t="s">
         <v>132</v>
       </c>
       <c r="D48" s="40" t="s">
@@ -3173,7 +3173,7 @@
       <c r="B49" s="38">
         <v>3</v>
       </c>
-      <c r="C49" s="74" t="s">
+      <c r="C49" s="55" t="s">
         <v>133</v>
       </c>
       <c r="D49" s="40" t="s">
@@ -3184,7 +3184,7 @@
       <c r="B50" s="38">
         <v>4</v>
       </c>
-      <c r="C50" s="74" t="s">
+      <c r="C50" s="55" t="s">
         <v>134</v>
       </c>
       <c r="D50" s="42" t="s">
@@ -3193,6 +3193,12 @@
     </row>
   </sheetData>
   <mergeCells count="16">
+    <mergeCell ref="B17:D17"/>
+    <mergeCell ref="B3:D3"/>
+    <mergeCell ref="B5:D5"/>
+    <mergeCell ref="B6:D6"/>
+    <mergeCell ref="B7:D7"/>
+    <mergeCell ref="B16:D16"/>
     <mergeCell ref="B36:D36"/>
     <mergeCell ref="B43:D43"/>
     <mergeCell ref="B44:D44"/>
@@ -3203,12 +3209,6 @@
     <mergeCell ref="B27:D27"/>
     <mergeCell ref="B34:D34"/>
     <mergeCell ref="B35:D35"/>
-    <mergeCell ref="B3:D3"/>
-    <mergeCell ref="B5:D5"/>
-    <mergeCell ref="B6:D6"/>
-    <mergeCell ref="B7:D7"/>
-    <mergeCell ref="B16:D16"/>
-    <mergeCell ref="B17:D17"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
@@ -3225,11 +3225,11 @@
   </cols>
   <sheetData>
     <row r="4" spans="2:4" ht="15.75">
-      <c r="B4" s="58" t="s">
+      <c r="B4" s="67" t="s">
         <v>94</v>
       </c>
-      <c r="C4" s="59"/>
-      <c r="D4" s="59"/>
+      <c r="C4" s="68"/>
+      <c r="D4" s="68"/>
     </row>
     <row r="5" spans="2:4">
       <c r="B5" s="1"/>
@@ -3237,25 +3237,25 @@
       <c r="D5" s="1"/>
     </row>
     <row r="6" spans="2:4">
-      <c r="B6" s="48" t="s">
+      <c r="B6" s="56" t="s">
         <v>95</v>
       </c>
-      <c r="C6" s="49"/>
-      <c r="D6" s="50"/>
+      <c r="C6" s="57"/>
+      <c r="D6" s="58"/>
     </row>
     <row r="7" spans="2:4">
-      <c r="B7" s="48" t="s">
-        <v>2</v>
-      </c>
-      <c r="C7" s="49"/>
-      <c r="D7" s="50"/>
+      <c r="B7" s="56" t="s">
+        <v>2</v>
+      </c>
+      <c r="C7" s="57"/>
+      <c r="D7" s="58"/>
     </row>
     <row r="8" spans="2:4" ht="249" customHeight="1">
-      <c r="B8" s="60" t="s">
+      <c r="B8" s="69" t="s">
         <v>96</v>
       </c>
-      <c r="C8" s="52"/>
-      <c r="D8" s="53"/>
+      <c r="C8" s="64"/>
+      <c r="D8" s="65"/>
     </row>
     <row r="9" spans="2:4">
       <c r="B9" s="43" t="s">
@@ -3313,25 +3313,25 @@
       </c>
     </row>
     <row r="16" spans="2:4">
-      <c r="B16" s="54" t="s">
+      <c r="B16" s="66" t="s">
         <v>101</v>
       </c>
-      <c r="C16" s="49"/>
-      <c r="D16" s="50"/>
+      <c r="C16" s="57"/>
+      <c r="D16" s="58"/>
     </row>
     <row r="17" spans="2:4">
-      <c r="B17" s="48" t="s">
-        <v>2</v>
-      </c>
-      <c r="C17" s="49"/>
-      <c r="D17" s="50"/>
+      <c r="B17" s="56" t="s">
+        <v>2</v>
+      </c>
+      <c r="C17" s="57"/>
+      <c r="D17" s="58"/>
     </row>
     <row r="18" spans="2:4" ht="248.25" customHeight="1">
-      <c r="B18" s="51" t="s">
+      <c r="B18" s="63" t="s">
         <v>102</v>
       </c>
-      <c r="C18" s="52"/>
-      <c r="D18" s="53"/>
+      <c r="C18" s="64"/>
+      <c r="D18" s="65"/>
     </row>
     <row r="19" spans="2:4">
       <c r="B19" s="43" t="s">
@@ -3383,25 +3383,25 @@
       <c r="D23" s="46"/>
     </row>
     <row r="26" spans="2:4">
-      <c r="B26" s="54" t="s">
+      <c r="B26" s="66" t="s">
         <v>106</v>
       </c>
-      <c r="C26" s="49"/>
-      <c r="D26" s="50"/>
+      <c r="C26" s="57"/>
+      <c r="D26" s="58"/>
     </row>
     <row r="27" spans="2:4">
-      <c r="B27" s="55" t="s">
-        <v>2</v>
-      </c>
-      <c r="C27" s="52"/>
-      <c r="D27" s="53"/>
+      <c r="B27" s="70" t="s">
+        <v>2</v>
+      </c>
+      <c r="C27" s="64"/>
+      <c r="D27" s="65"/>
     </row>
     <row r="28" spans="2:4" ht="246" customHeight="1">
-      <c r="B28" s="56" t="s">
+      <c r="B28" s="71" t="s">
         <v>105</v>
       </c>
-      <c r="C28" s="57"/>
-      <c r="D28" s="57"/>
+      <c r="C28" s="72"/>
+      <c r="D28" s="72"/>
     </row>
     <row r="29" spans="2:4">
       <c r="B29" s="43" t="s">
@@ -3460,16 +3460,16 @@
     </row>
   </sheetData>
   <mergeCells count="10">
+    <mergeCell ref="B17:D17"/>
+    <mergeCell ref="B18:D18"/>
+    <mergeCell ref="B26:D26"/>
+    <mergeCell ref="B27:D27"/>
+    <mergeCell ref="B28:D28"/>
     <mergeCell ref="B4:D4"/>
     <mergeCell ref="B6:D6"/>
     <mergeCell ref="B7:D7"/>
     <mergeCell ref="B8:D8"/>
     <mergeCell ref="B16:D16"/>
-    <mergeCell ref="B17:D17"/>
-    <mergeCell ref="B18:D18"/>
-    <mergeCell ref="B26:D26"/>
-    <mergeCell ref="B27:D27"/>
-    <mergeCell ref="B28:D28"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
@@ -3489,11 +3489,11 @@
   </cols>
   <sheetData>
     <row r="3" spans="2:4">
-      <c r="B3" s="58" t="s">
+      <c r="B3" s="67" t="s">
         <v>74</v>
       </c>
-      <c r="C3" s="59"/>
-      <c r="D3" s="59"/>
+      <c r="C3" s="68"/>
+      <c r="D3" s="68"/>
     </row>
     <row r="4" spans="2:4" ht="12.75">
       <c r="B4" s="1"/>
@@ -3501,25 +3501,25 @@
       <c r="D4" s="1"/>
     </row>
     <row r="5" spans="2:4" ht="12.75">
-      <c r="B5" s="48" t="s">
+      <c r="B5" s="56" t="s">
         <v>75</v>
       </c>
-      <c r="C5" s="49"/>
-      <c r="D5" s="50"/>
+      <c r="C5" s="57"/>
+      <c r="D5" s="58"/>
     </row>
     <row r="6" spans="2:4" ht="12.75">
-      <c r="B6" s="48" t="s">
-        <v>2</v>
-      </c>
-      <c r="C6" s="49"/>
-      <c r="D6" s="50"/>
+      <c r="B6" s="56" t="s">
+        <v>2</v>
+      </c>
+      <c r="C6" s="57"/>
+      <c r="D6" s="58"/>
     </row>
     <row r="7" spans="2:4" ht="229.5" customHeight="1">
-      <c r="B7" s="66" t="s">
+      <c r="B7" s="59" t="s">
         <v>76</v>
       </c>
-      <c r="C7" s="49"/>
-      <c r="D7" s="50"/>
+      <c r="C7" s="57"/>
+      <c r="D7" s="58"/>
     </row>
     <row r="8" spans="2:4" ht="12.75">
       <c r="B8" s="26" t="s">
@@ -3577,25 +3577,25 @@
       </c>
     </row>
     <row r="16" spans="2:4" ht="12.75">
-      <c r="B16" s="48" t="s">
+      <c r="B16" s="56" t="s">
         <v>80</v>
       </c>
-      <c r="C16" s="49"/>
-      <c r="D16" s="50"/>
+      <c r="C16" s="57"/>
+      <c r="D16" s="58"/>
     </row>
     <row r="17" spans="2:4" ht="12.75">
-      <c r="B17" s="48" t="s">
-        <v>2</v>
-      </c>
-      <c r="C17" s="49"/>
-      <c r="D17" s="50"/>
+      <c r="B17" s="56" t="s">
+        <v>2</v>
+      </c>
+      <c r="C17" s="57"/>
+      <c r="D17" s="58"/>
     </row>
     <row r="18" spans="2:4" ht="174" customHeight="1">
-      <c r="B18" s="66" t="s">
+      <c r="B18" s="59" t="s">
         <v>81</v>
       </c>
-      <c r="C18" s="49"/>
-      <c r="D18" s="50"/>
+      <c r="C18" s="57"/>
+      <c r="D18" s="58"/>
     </row>
     <row r="19" spans="2:4" ht="12.75">
       <c r="B19" s="26" t="s">
@@ -3653,25 +3653,25 @@
       </c>
     </row>
     <row r="27" spans="2:4" ht="12.75">
-      <c r="B27" s="48" t="s">
+      <c r="B27" s="56" t="s">
         <v>85</v>
       </c>
-      <c r="C27" s="49"/>
-      <c r="D27" s="50"/>
+      <c r="C27" s="57"/>
+      <c r="D27" s="58"/>
     </row>
     <row r="28" spans="2:4" ht="12.75">
-      <c r="B28" s="48" t="s">
-        <v>2</v>
-      </c>
-      <c r="C28" s="49"/>
-      <c r="D28" s="50"/>
+      <c r="B28" s="56" t="s">
+        <v>2</v>
+      </c>
+      <c r="C28" s="57"/>
+      <c r="D28" s="58"/>
     </row>
     <row r="29" spans="2:4" ht="93.75" customHeight="1">
-      <c r="B29" s="66" t="s">
+      <c r="B29" s="59" t="s">
         <v>86</v>
       </c>
-      <c r="C29" s="49"/>
-      <c r="D29" s="50"/>
+      <c r="C29" s="57"/>
+      <c r="D29" s="58"/>
     </row>
     <row r="30" spans="2:4" ht="12.75">
       <c r="B30" s="33" t="s">
@@ -3723,25 +3723,25 @@
       <c r="D34" s="37"/>
     </row>
     <row r="37" spans="2:4" ht="12.75">
-      <c r="B37" s="48" t="s">
+      <c r="B37" s="56" t="s">
         <v>89</v>
       </c>
-      <c r="C37" s="49"/>
-      <c r="D37" s="50"/>
+      <c r="C37" s="57"/>
+      <c r="D37" s="58"/>
     </row>
     <row r="38" spans="2:4" ht="12.75">
-      <c r="B38" s="48" t="s">
-        <v>2</v>
-      </c>
-      <c r="C38" s="49"/>
-      <c r="D38" s="50"/>
+      <c r="B38" s="56" t="s">
+        <v>2</v>
+      </c>
+      <c r="C38" s="57"/>
+      <c r="D38" s="58"/>
     </row>
     <row r="39" spans="2:4" ht="226.5" customHeight="1">
-      <c r="B39" s="66" t="s">
+      <c r="B39" s="59" t="s">
         <v>90</v>
       </c>
-      <c r="C39" s="49"/>
-      <c r="D39" s="50"/>
+      <c r="C39" s="57"/>
+      <c r="D39" s="58"/>
     </row>
     <row r="40" spans="2:4" ht="12.75">
       <c r="B40" s="26" t="s">

--- a/Proyecto/docs/Pruebas de Caja Negra_Blanca/Pruebas de Caja Blanca-SistemaPOS.xlsx
+++ b/Proyecto/docs/Pruebas de Caja Negra_Blanca/Pruebas de Caja Blanca-SistemaPOS.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="24334"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29929"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/01f32f4e8c9e178e/Desktop/Analisis y Diseño/36289_AnalisisYDisenoDeSistemas/Proyecto/docs/Pruebas de Caja Negra_Blanca/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="263" documentId="11_94B3DA253D63A0DE445D4A83045116E5BA157345" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{97E470D3-C7FC-4742-A0A7-1ADB363A31FB}"/>
+  <xr:revisionPtr revIDLastSave="268" documentId="11_94B3DA253D63A0DE445D4A83045116E5BA157345" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{F93F91EE-E161-44B5-A001-4D3034166A34}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11040" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Usuario - Administrador" sheetId="1" r:id="rId1"/>
@@ -29,9 +29,6 @@
         <xcalcf:feature name="microsoft.com:CNMTM"/>
         <xcalcf:feature name="microsoft.com:LET_WF"/>
       </xcalcf:calcFeatures>
-    </ext>
-    <ext xmlns:xlwcv="http://schemas.microsoft.com/office/spreadsheetml/2024/workbookCompatibilityVersion" uri="{D14903EA-33C4-47F7-8F05-3474C54BE107}">
-      <xlwcv:version setVersion="1"/>
     </ext>
   </extLst>
 </workbook>
@@ -1355,7 +1352,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="73">
+  <cellXfs count="72">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
     <xf numFmtId="0" fontId="3" fillId="2" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -1481,39 +1478,38 @@
     <xf numFmtId="0" fontId="22" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="18" fillId="8" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="18" fillId="8" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="22" fillId="8" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="22" fillId="8" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="9" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="5" fillId="9" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="22" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="18" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="3" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="6" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="5" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="3" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="2" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="17" fillId="3" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="3" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="21" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="5" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="2" fillId="3" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="17" fillId="3" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="2" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
@@ -1752,11 +1748,11 @@
   </cols>
   <sheetData>
     <row r="2" spans="2:4">
-      <c r="B2" s="67" t="s">
+      <c r="B2" s="60" t="s">
         <v>0</v>
       </c>
-      <c r="C2" s="68"/>
-      <c r="D2" s="68"/>
+      <c r="C2" s="61"/>
+      <c r="D2" s="61"/>
     </row>
     <row r="3" spans="2:4" ht="12.75">
       <c r="B3" s="1"/>
@@ -1764,21 +1760,21 @@
       <c r="D3" s="1"/>
     </row>
     <row r="4" spans="2:4" ht="12.75">
-      <c r="B4" s="56" t="s">
+      <c r="B4" s="62" t="s">
         <v>1</v>
       </c>
       <c r="C4" s="57"/>
       <c r="D4" s="58"/>
     </row>
     <row r="5" spans="2:4" ht="12.75">
-      <c r="B5" s="56" t="s">
+      <c r="B5" s="62" t="s">
         <v>2</v>
       </c>
       <c r="C5" s="57"/>
       <c r="D5" s="58"/>
     </row>
     <row r="6" spans="2:4" ht="192" customHeight="1">
-      <c r="B6" s="59" t="s">
+      <c r="B6" s="63" t="s">
         <v>3</v>
       </c>
       <c r="C6" s="57"/>
@@ -1840,21 +1836,21 @@
       </c>
     </row>
     <row r="15" spans="2:4" ht="12.75">
-      <c r="B15" s="60" t="s">
+      <c r="B15" s="56" t="s">
         <v>13</v>
       </c>
       <c r="C15" s="57"/>
       <c r="D15" s="58"/>
     </row>
     <row r="16" spans="2:4" ht="22.5" customHeight="1">
-      <c r="B16" s="60" t="s">
+      <c r="B16" s="56" t="s">
         <v>2</v>
       </c>
       <c r="C16" s="57"/>
       <c r="D16" s="58"/>
     </row>
     <row r="17" spans="2:4" ht="177" customHeight="1">
-      <c r="B17" s="61" t="s">
+      <c r="B17" s="59" t="s">
         <v>14</v>
       </c>
       <c r="C17" s="57"/>
@@ -1905,21 +1901,21 @@
       </c>
     </row>
     <row r="25" spans="2:4" ht="12.75">
-      <c r="B25" s="60" t="s">
+      <c r="B25" s="56" t="s">
         <v>18</v>
       </c>
       <c r="C25" s="57"/>
       <c r="D25" s="58"/>
     </row>
     <row r="26" spans="2:4" ht="12.75">
-      <c r="B26" s="60" t="s">
+      <c r="B26" s="56" t="s">
         <v>2</v>
       </c>
       <c r="C26" s="57"/>
       <c r="D26" s="58"/>
     </row>
-    <row r="27" spans="2:4" ht="197.25" customHeight="1">
-      <c r="B27" s="61" t="s">
+    <row r="27" spans="2:4" ht="213" customHeight="1">
+      <c r="B27" s="59" t="s">
         <v>19</v>
       </c>
       <c r="C27" s="57"/>
@@ -1981,21 +1977,21 @@
       </c>
     </row>
     <row r="34" spans="2:4" ht="12.75">
-      <c r="B34" s="60" t="s">
+      <c r="B34" s="56" t="s">
         <v>24</v>
       </c>
       <c r="C34" s="57"/>
       <c r="D34" s="58"/>
     </row>
     <row r="35" spans="2:4" ht="12.75">
-      <c r="B35" s="60" t="s">
+      <c r="B35" s="56" t="s">
         <v>2</v>
       </c>
       <c r="C35" s="57"/>
       <c r="D35" s="58"/>
     </row>
-    <row r="36" spans="2:4" ht="12.75">
-      <c r="B36" s="62" t="s">
+    <row r="36" spans="2:4" ht="144" customHeight="1">
+      <c r="B36" s="59" t="s">
         <v>25</v>
       </c>
       <c r="C36" s="57"/>
@@ -2046,21 +2042,21 @@
       </c>
     </row>
     <row r="43" spans="2:4" ht="12.75">
-      <c r="B43" s="60" t="s">
+      <c r="B43" s="56" t="s">
         <v>28</v>
       </c>
       <c r="C43" s="57"/>
       <c r="D43" s="58"/>
     </row>
     <row r="44" spans="2:4" ht="12.75">
-      <c r="B44" s="60" t="s">
+      <c r="B44" s="56" t="s">
         <v>2</v>
       </c>
       <c r="C44" s="57"/>
       <c r="D44" s="58"/>
     </row>
     <row r="45" spans="2:4" ht="150" customHeight="1">
-      <c r="B45" s="61" t="s">
+      <c r="B45" s="59" t="s">
         <v>29</v>
       </c>
       <c r="C45" s="57"/>
@@ -2111,21 +2107,21 @@
       </c>
     </row>
     <row r="52" spans="2:4" ht="12.75">
-      <c r="B52" s="60" t="s">
+      <c r="B52" s="56" t="s">
         <v>33</v>
       </c>
       <c r="C52" s="57"/>
       <c r="D52" s="58"/>
     </row>
     <row r="53" spans="2:4" ht="12.75">
-      <c r="B53" s="60" t="s">
+      <c r="B53" s="56" t="s">
         <v>2</v>
       </c>
       <c r="C53" s="57"/>
       <c r="D53" s="58"/>
     </row>
     <row r="54" spans="2:4" ht="99" customHeight="1">
-      <c r="B54" s="61" t="s">
+      <c r="B54" s="59" t="s">
         <v>34</v>
       </c>
       <c r="C54" s="57"/>
@@ -2176,21 +2172,21 @@
       </c>
     </row>
     <row r="61" spans="2:4" ht="12.75">
-      <c r="B61" s="60" t="s">
+      <c r="B61" s="56" t="s">
         <v>37</v>
       </c>
       <c r="C61" s="57"/>
       <c r="D61" s="58"/>
     </row>
     <row r="62" spans="2:4" ht="12.75">
-      <c r="B62" s="60" t="s">
+      <c r="B62" s="56" t="s">
         <v>2</v>
       </c>
       <c r="C62" s="57"/>
       <c r="D62" s="58"/>
     </row>
     <row r="63" spans="2:4" ht="227.25" customHeight="1">
-      <c r="B63" s="61" t="s">
+      <c r="B63" s="59" t="s">
         <v>38</v>
       </c>
       <c r="C63" s="57"/>
@@ -2252,21 +2248,21 @@
       </c>
     </row>
     <row r="71" spans="2:4" ht="12.75">
-      <c r="B71" s="60" t="s">
+      <c r="B71" s="56" t="s">
         <v>43</v>
       </c>
       <c r="C71" s="57"/>
       <c r="D71" s="58"/>
     </row>
     <row r="72" spans="2:4" ht="12.75">
-      <c r="B72" s="60" t="s">
+      <c r="B72" s="56" t="s">
         <v>2</v>
       </c>
       <c r="C72" s="57"/>
       <c r="D72" s="58"/>
     </row>
     <row r="73" spans="2:4" ht="96" customHeight="1">
-      <c r="B73" s="61" t="s">
+      <c r="B73" s="59" t="s">
         <v>44</v>
       </c>
       <c r="C73" s="57"/>
@@ -2318,6 +2314,21 @@
     </row>
   </sheetData>
   <mergeCells count="25">
+    <mergeCell ref="B2:D2"/>
+    <mergeCell ref="B4:D4"/>
+    <mergeCell ref="B5:D5"/>
+    <mergeCell ref="B6:D6"/>
+    <mergeCell ref="B15:D15"/>
+    <mergeCell ref="B16:D16"/>
+    <mergeCell ref="B17:D17"/>
+    <mergeCell ref="B25:D25"/>
+    <mergeCell ref="B26:D26"/>
+    <mergeCell ref="B27:D27"/>
+    <mergeCell ref="B34:D34"/>
+    <mergeCell ref="B35:D35"/>
+    <mergeCell ref="B36:D36"/>
+    <mergeCell ref="B43:D43"/>
+    <mergeCell ref="B63:D63"/>
     <mergeCell ref="B71:D71"/>
     <mergeCell ref="B72:D72"/>
     <mergeCell ref="B73:D73"/>
@@ -2328,21 +2339,6 @@
     <mergeCell ref="B54:D54"/>
     <mergeCell ref="B61:D61"/>
     <mergeCell ref="B62:D62"/>
-    <mergeCell ref="B34:D34"/>
-    <mergeCell ref="B35:D35"/>
-    <mergeCell ref="B36:D36"/>
-    <mergeCell ref="B43:D43"/>
-    <mergeCell ref="B63:D63"/>
-    <mergeCell ref="B16:D16"/>
-    <mergeCell ref="B17:D17"/>
-    <mergeCell ref="B25:D25"/>
-    <mergeCell ref="B26:D26"/>
-    <mergeCell ref="B27:D27"/>
-    <mergeCell ref="B2:D2"/>
-    <mergeCell ref="B4:D4"/>
-    <mergeCell ref="B5:D5"/>
-    <mergeCell ref="B6:D6"/>
-    <mergeCell ref="B15:D15"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
@@ -2363,11 +2359,11 @@
   </cols>
   <sheetData>
     <row r="2" spans="2:4">
-      <c r="B2" s="67" t="s">
+      <c r="B2" s="60" t="s">
         <v>47</v>
       </c>
-      <c r="C2" s="68"/>
-      <c r="D2" s="68"/>
+      <c r="C2" s="61"/>
+      <c r="D2" s="61"/>
     </row>
     <row r="3" spans="2:4" ht="12.75">
       <c r="B3" s="1"/>
@@ -2375,21 +2371,21 @@
       <c r="D3" s="1"/>
     </row>
     <row r="4" spans="2:4" ht="12.75">
-      <c r="B4" s="56" t="s">
+      <c r="B4" s="62" t="s">
         <v>1</v>
       </c>
       <c r="C4" s="57"/>
       <c r="D4" s="58"/>
     </row>
     <row r="5" spans="2:4" ht="12.75">
-      <c r="B5" s="56" t="s">
+      <c r="B5" s="62" t="s">
         <v>2</v>
       </c>
       <c r="C5" s="57"/>
       <c r="D5" s="58"/>
     </row>
     <row r="6" spans="2:4" ht="184.5" customHeight="1">
-      <c r="B6" s="59" t="s">
+      <c r="B6" s="63" t="s">
         <v>3</v>
       </c>
       <c r="C6" s="57"/>
@@ -2451,21 +2447,21 @@
       </c>
     </row>
     <row r="15" spans="2:4" ht="12.75">
-      <c r="B15" s="56" t="s">
+      <c r="B15" s="62" t="s">
         <v>48</v>
       </c>
       <c r="C15" s="57"/>
       <c r="D15" s="58"/>
     </row>
     <row r="16" spans="2:4" ht="12.75">
-      <c r="B16" s="56" t="s">
+      <c r="B16" s="62" t="s">
         <v>2</v>
       </c>
       <c r="C16" s="57"/>
       <c r="D16" s="58"/>
     </row>
     <row r="17" spans="2:4" ht="222.75" customHeight="1">
-      <c r="B17" s="59" t="s">
+      <c r="B17" s="63" t="s">
         <v>49</v>
       </c>
       <c r="C17" s="57"/>
@@ -2527,21 +2523,21 @@
       </c>
     </row>
     <row r="26" spans="2:4" ht="12.75">
-      <c r="B26" s="56" t="s">
+      <c r="B26" s="62" t="s">
         <v>54</v>
       </c>
       <c r="C26" s="57"/>
       <c r="D26" s="58"/>
     </row>
     <row r="27" spans="2:4" ht="12.75">
-      <c r="B27" s="56" t="s">
+      <c r="B27" s="62" t="s">
         <v>2</v>
       </c>
       <c r="C27" s="57"/>
       <c r="D27" s="58"/>
     </row>
     <row r="28" spans="2:4" ht="138" customHeight="1">
-      <c r="B28" s="59" t="s">
+      <c r="B28" s="63" t="s">
         <v>55</v>
       </c>
       <c r="C28" s="57"/>
@@ -2597,21 +2593,21 @@
       <c r="D33" s="32"/>
     </row>
     <row r="36" spans="2:4" ht="12.75">
-      <c r="B36" s="56" t="s">
+      <c r="B36" s="62" t="s">
         <v>59</v>
       </c>
       <c r="C36" s="57"/>
       <c r="D36" s="58"/>
     </row>
     <row r="37" spans="2:4" ht="16.5" customHeight="1">
-      <c r="B37" s="56" t="s">
+      <c r="B37" s="62" t="s">
         <v>2</v>
       </c>
       <c r="C37" s="57"/>
       <c r="D37" s="58"/>
     </row>
     <row r="38" spans="2:4" ht="212.25" customHeight="1">
-      <c r="B38" s="59" t="s">
+      <c r="B38" s="63" t="s">
         <v>60</v>
       </c>
       <c r="C38" s="57"/>
@@ -2662,21 +2658,21 @@
       </c>
     </row>
     <row r="46" spans="2:4" ht="12.75">
-      <c r="B46" s="56" t="s">
+      <c r="B46" s="62" t="s">
         <v>64</v>
       </c>
       <c r="C46" s="57"/>
       <c r="D46" s="58"/>
     </row>
     <row r="47" spans="2:4" ht="12.75">
-      <c r="B47" s="56" t="s">
+      <c r="B47" s="62" t="s">
         <v>2</v>
       </c>
       <c r="C47" s="57"/>
       <c r="D47" s="58"/>
     </row>
     <row r="48" spans="2:4" ht="139.5" customHeight="1">
-      <c r="B48" s="59" t="s">
+      <c r="B48" s="63" t="s">
         <v>65</v>
       </c>
       <c r="C48" s="57"/>
@@ -2727,21 +2723,21 @@
       </c>
     </row>
     <row r="56" spans="2:4" ht="12.75">
-      <c r="B56" s="56" t="s">
+      <c r="B56" s="62" t="s">
         <v>69</v>
       </c>
       <c r="C56" s="57"/>
       <c r="D56" s="58"/>
     </row>
     <row r="57" spans="2:4" ht="12.75">
-      <c r="B57" s="56" t="s">
+      <c r="B57" s="62" t="s">
         <v>2</v>
       </c>
       <c r="C57" s="57"/>
       <c r="D57" s="58"/>
     </row>
     <row r="58" spans="2:4" ht="193.5" customHeight="1">
-      <c r="B58" s="59" t="s">
+      <c r="B58" s="63" t="s">
         <v>70</v>
       </c>
       <c r="C58" s="57"/>
@@ -2793,6 +2789,16 @@
     </row>
   </sheetData>
   <mergeCells count="19">
+    <mergeCell ref="B2:D2"/>
+    <mergeCell ref="B4:D4"/>
+    <mergeCell ref="B5:D5"/>
+    <mergeCell ref="B6:D6"/>
+    <mergeCell ref="B15:D15"/>
+    <mergeCell ref="B16:D16"/>
+    <mergeCell ref="B17:D17"/>
+    <mergeCell ref="B47:D47"/>
+    <mergeCell ref="B48:D48"/>
+    <mergeCell ref="B56:D56"/>
     <mergeCell ref="B57:D57"/>
     <mergeCell ref="B58:D58"/>
     <mergeCell ref="B26:D26"/>
@@ -2802,16 +2808,6 @@
     <mergeCell ref="B37:D37"/>
     <mergeCell ref="B38:D38"/>
     <mergeCell ref="B46:D46"/>
-    <mergeCell ref="B16:D16"/>
-    <mergeCell ref="B17:D17"/>
-    <mergeCell ref="B47:D47"/>
-    <mergeCell ref="B48:D48"/>
-    <mergeCell ref="B56:D56"/>
-    <mergeCell ref="B2:D2"/>
-    <mergeCell ref="B4:D4"/>
-    <mergeCell ref="B5:D5"/>
-    <mergeCell ref="B6:D6"/>
-    <mergeCell ref="B15:D15"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
@@ -2828,11 +2824,11 @@
   </cols>
   <sheetData>
     <row r="3" spans="2:4" ht="15.75">
-      <c r="B3" s="67" t="s">
+      <c r="B3" s="60" t="s">
         <v>135</v>
       </c>
-      <c r="C3" s="68"/>
-      <c r="D3" s="68"/>
+      <c r="C3" s="61"/>
+      <c r="D3" s="61"/>
     </row>
     <row r="4" spans="2:4">
       <c r="B4" s="1"/>
@@ -2840,25 +2836,25 @@
       <c r="D4" s="1"/>
     </row>
     <row r="5" spans="2:4">
-      <c r="B5" s="56" t="s">
+      <c r="B5" s="62" t="s">
         <v>111</v>
       </c>
       <c r="C5" s="57"/>
       <c r="D5" s="58"/>
     </row>
     <row r="6" spans="2:4" ht="15.75" customHeight="1">
-      <c r="B6" s="56" t="s">
+      <c r="B6" s="62" t="s">
         <v>2</v>
       </c>
       <c r="C6" s="57"/>
       <c r="D6" s="58"/>
     </row>
     <row r="7" spans="2:4" ht="288.75" customHeight="1">
-      <c r="B7" s="69" t="s">
+      <c r="B7" s="64" t="s">
         <v>112</v>
       </c>
-      <c r="C7" s="64"/>
-      <c r="D7" s="65"/>
+      <c r="C7" s="65"/>
+      <c r="D7" s="66"/>
     </row>
     <row r="8" spans="2:4">
       <c r="B8" s="43" t="s">
@@ -2916,25 +2912,25 @@
       </c>
     </row>
     <row r="16" spans="2:4">
-      <c r="B16" s="66" t="s">
+      <c r="B16" s="67" t="s">
         <v>121</v>
       </c>
       <c r="C16" s="57"/>
       <c r="D16" s="58"/>
     </row>
     <row r="17" spans="2:4" ht="18.75" customHeight="1">
-      <c r="B17" s="56" t="s">
+      <c r="B17" s="62" t="s">
         <v>2</v>
       </c>
       <c r="C17" s="57"/>
       <c r="D17" s="58"/>
     </row>
     <row r="18" spans="2:4" ht="132" customHeight="1">
-      <c r="B18" s="63" t="s">
+      <c r="B18" s="68" t="s">
         <v>117</v>
       </c>
-      <c r="C18" s="64"/>
-      <c r="D18" s="65"/>
+      <c r="C18" s="65"/>
+      <c r="D18" s="66"/>
     </row>
     <row r="19" spans="2:4">
       <c r="B19" s="43" t="s">
@@ -2986,25 +2982,25 @@
       <c r="D23" s="53"/>
     </row>
     <row r="25" spans="2:4">
-      <c r="B25" s="66" t="s">
+      <c r="B25" s="67" t="s">
         <v>126</v>
       </c>
       <c r="C25" s="57"/>
       <c r="D25" s="58"/>
     </row>
     <row r="26" spans="2:4" ht="13.5" customHeight="1">
-      <c r="B26" s="56" t="s">
+      <c r="B26" s="62" t="s">
         <v>2</v>
       </c>
       <c r="C26" s="57"/>
       <c r="D26" s="58"/>
     </row>
     <row r="27" spans="2:4" ht="168" customHeight="1">
-      <c r="B27" s="63" t="s">
+      <c r="B27" s="68" t="s">
         <v>125</v>
       </c>
-      <c r="C27" s="64"/>
-      <c r="D27" s="65"/>
+      <c r="C27" s="65"/>
+      <c r="D27" s="66"/>
     </row>
     <row r="28" spans="2:4">
       <c r="B28" s="43" t="s">
@@ -3051,25 +3047,25 @@
       </c>
     </row>
     <row r="34" spans="2:4">
-      <c r="B34" s="66" t="s">
+      <c r="B34" s="67" t="s">
         <v>130</v>
       </c>
       <c r="C34" s="57"/>
       <c r="D34" s="58"/>
     </row>
     <row r="35" spans="2:4">
-      <c r="B35" s="56" t="s">
+      <c r="B35" s="62" t="s">
         <v>2</v>
       </c>
       <c r="C35" s="57"/>
       <c r="D35" s="58"/>
     </row>
     <row r="36" spans="2:4" ht="185.25" customHeight="1">
-      <c r="B36" s="63" t="s">
+      <c r="B36" s="68" t="s">
         <v>127</v>
       </c>
-      <c r="C36" s="64"/>
-      <c r="D36" s="65"/>
+      <c r="C36" s="65"/>
+      <c r="D36" s="66"/>
     </row>
     <row r="37" spans="2:4">
       <c r="B37" s="43" t="s">
@@ -3116,25 +3112,25 @@
       </c>
     </row>
     <row r="43" spans="2:4">
-      <c r="B43" s="66" t="s">
+      <c r="B43" s="67" t="s">
         <v>111</v>
       </c>
       <c r="C43" s="57"/>
       <c r="D43" s="58"/>
     </row>
     <row r="44" spans="2:4">
-      <c r="B44" s="56" t="s">
+      <c r="B44" s="62" t="s">
         <v>2</v>
       </c>
       <c r="C44" s="57"/>
       <c r="D44" s="58"/>
     </row>
     <row r="45" spans="2:4" ht="222.75" customHeight="1">
-      <c r="B45" s="63" t="s">
+      <c r="B45" s="68" t="s">
         <v>131</v>
       </c>
-      <c r="C45" s="64"/>
-      <c r="D45" s="65"/>
+      <c r="C45" s="65"/>
+      <c r="D45" s="66"/>
     </row>
     <row r="46" spans="2:4">
       <c r="B46" s="43" t="s">
@@ -3193,12 +3189,6 @@
     </row>
   </sheetData>
   <mergeCells count="16">
-    <mergeCell ref="B17:D17"/>
-    <mergeCell ref="B3:D3"/>
-    <mergeCell ref="B5:D5"/>
-    <mergeCell ref="B6:D6"/>
-    <mergeCell ref="B7:D7"/>
-    <mergeCell ref="B16:D16"/>
     <mergeCell ref="B36:D36"/>
     <mergeCell ref="B43:D43"/>
     <mergeCell ref="B44:D44"/>
@@ -3209,6 +3199,12 @@
     <mergeCell ref="B27:D27"/>
     <mergeCell ref="B34:D34"/>
     <mergeCell ref="B35:D35"/>
+    <mergeCell ref="B17:D17"/>
+    <mergeCell ref="B3:D3"/>
+    <mergeCell ref="B5:D5"/>
+    <mergeCell ref="B6:D6"/>
+    <mergeCell ref="B7:D7"/>
+    <mergeCell ref="B16:D16"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
@@ -3225,11 +3221,11 @@
   </cols>
   <sheetData>
     <row r="4" spans="2:4" ht="15.75">
-      <c r="B4" s="67" t="s">
+      <c r="B4" s="60" t="s">
         <v>94</v>
       </c>
-      <c r="C4" s="68"/>
-      <c r="D4" s="68"/>
+      <c r="C4" s="61"/>
+      <c r="D4" s="61"/>
     </row>
     <row r="5" spans="2:4">
       <c r="B5" s="1"/>
@@ -3237,25 +3233,25 @@
       <c r="D5" s="1"/>
     </row>
     <row r="6" spans="2:4">
-      <c r="B6" s="56" t="s">
+      <c r="B6" s="62" t="s">
         <v>95</v>
       </c>
       <c r="C6" s="57"/>
       <c r="D6" s="58"/>
     </row>
     <row r="7" spans="2:4">
-      <c r="B7" s="56" t="s">
+      <c r="B7" s="62" t="s">
         <v>2</v>
       </c>
       <c r="C7" s="57"/>
       <c r="D7" s="58"/>
     </row>
     <row r="8" spans="2:4" ht="249" customHeight="1">
-      <c r="B8" s="69" t="s">
+      <c r="B8" s="64" t="s">
         <v>96</v>
       </c>
-      <c r="C8" s="64"/>
-      <c r="D8" s="65"/>
+      <c r="C8" s="65"/>
+      <c r="D8" s="66"/>
     </row>
     <row r="9" spans="2:4">
       <c r="B9" s="43" t="s">
@@ -3313,25 +3309,25 @@
       </c>
     </row>
     <row r="16" spans="2:4">
-      <c r="B16" s="66" t="s">
+      <c r="B16" s="67" t="s">
         <v>101</v>
       </c>
       <c r="C16" s="57"/>
       <c r="D16" s="58"/>
     </row>
     <row r="17" spans="2:4">
-      <c r="B17" s="56" t="s">
+      <c r="B17" s="62" t="s">
         <v>2</v>
       </c>
       <c r="C17" s="57"/>
       <c r="D17" s="58"/>
     </row>
     <row r="18" spans="2:4" ht="248.25" customHeight="1">
-      <c r="B18" s="63" t="s">
+      <c r="B18" s="68" t="s">
         <v>102</v>
       </c>
-      <c r="C18" s="64"/>
-      <c r="D18" s="65"/>
+      <c r="C18" s="65"/>
+      <c r="D18" s="66"/>
     </row>
     <row r="19" spans="2:4">
       <c r="B19" s="43" t="s">
@@ -3383,25 +3379,25 @@
       <c r="D23" s="46"/>
     </row>
     <row r="26" spans="2:4">
-      <c r="B26" s="66" t="s">
+      <c r="B26" s="67" t="s">
         <v>106</v>
       </c>
       <c r="C26" s="57"/>
       <c r="D26" s="58"/>
     </row>
     <row r="27" spans="2:4">
-      <c r="B27" s="70" t="s">
-        <v>2</v>
-      </c>
-      <c r="C27" s="64"/>
-      <c r="D27" s="65"/>
+      <c r="B27" s="69" t="s">
+        <v>2</v>
+      </c>
+      <c r="C27" s="65"/>
+      <c r="D27" s="66"/>
     </row>
     <row r="28" spans="2:4" ht="246" customHeight="1">
-      <c r="B28" s="71" t="s">
+      <c r="B28" s="70" t="s">
         <v>105</v>
       </c>
-      <c r="C28" s="72"/>
-      <c r="D28" s="72"/>
+      <c r="C28" s="71"/>
+      <c r="D28" s="71"/>
     </row>
     <row r="29" spans="2:4">
       <c r="B29" s="43" t="s">
@@ -3460,16 +3456,16 @@
     </row>
   </sheetData>
   <mergeCells count="10">
+    <mergeCell ref="B4:D4"/>
+    <mergeCell ref="B6:D6"/>
+    <mergeCell ref="B7:D7"/>
+    <mergeCell ref="B8:D8"/>
+    <mergeCell ref="B16:D16"/>
     <mergeCell ref="B17:D17"/>
     <mergeCell ref="B18:D18"/>
     <mergeCell ref="B26:D26"/>
     <mergeCell ref="B27:D27"/>
     <mergeCell ref="B28:D28"/>
-    <mergeCell ref="B4:D4"/>
-    <mergeCell ref="B6:D6"/>
-    <mergeCell ref="B7:D7"/>
-    <mergeCell ref="B8:D8"/>
-    <mergeCell ref="B16:D16"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
@@ -3489,11 +3485,11 @@
   </cols>
   <sheetData>
     <row r="3" spans="2:4">
-      <c r="B3" s="67" t="s">
+      <c r="B3" s="60" t="s">
         <v>74</v>
       </c>
-      <c r="C3" s="68"/>
-      <c r="D3" s="68"/>
+      <c r="C3" s="61"/>
+      <c r="D3" s="61"/>
     </row>
     <row r="4" spans="2:4" ht="12.75">
       <c r="B4" s="1"/>
@@ -3501,21 +3497,21 @@
       <c r="D4" s="1"/>
     </row>
     <row r="5" spans="2:4" ht="12.75">
-      <c r="B5" s="56" t="s">
+      <c r="B5" s="62" t="s">
         <v>75</v>
       </c>
       <c r="C5" s="57"/>
       <c r="D5" s="58"/>
     </row>
     <row r="6" spans="2:4" ht="12.75">
-      <c r="B6" s="56" t="s">
+      <c r="B6" s="62" t="s">
         <v>2</v>
       </c>
       <c r="C6" s="57"/>
       <c r="D6" s="58"/>
     </row>
     <row r="7" spans="2:4" ht="229.5" customHeight="1">
-      <c r="B7" s="59" t="s">
+      <c r="B7" s="63" t="s">
         <v>76</v>
       </c>
       <c r="C7" s="57"/>
@@ -3577,21 +3573,21 @@
       </c>
     </row>
     <row r="16" spans="2:4" ht="12.75">
-      <c r="B16" s="56" t="s">
+      <c r="B16" s="62" t="s">
         <v>80</v>
       </c>
       <c r="C16" s="57"/>
       <c r="D16" s="58"/>
     </row>
     <row r="17" spans="2:4" ht="12.75">
-      <c r="B17" s="56" t="s">
+      <c r="B17" s="62" t="s">
         <v>2</v>
       </c>
       <c r="C17" s="57"/>
       <c r="D17" s="58"/>
     </row>
     <row r="18" spans="2:4" ht="174" customHeight="1">
-      <c r="B18" s="59" t="s">
+      <c r="B18" s="63" t="s">
         <v>81</v>
       </c>
       <c r="C18" s="57"/>
@@ -3653,21 +3649,21 @@
       </c>
     </row>
     <row r="27" spans="2:4" ht="12.75">
-      <c r="B27" s="56" t="s">
+      <c r="B27" s="62" t="s">
         <v>85</v>
       </c>
       <c r="C27" s="57"/>
       <c r="D27" s="58"/>
     </row>
     <row r="28" spans="2:4" ht="12.75">
-      <c r="B28" s="56" t="s">
+      <c r="B28" s="62" t="s">
         <v>2</v>
       </c>
       <c r="C28" s="57"/>
       <c r="D28" s="58"/>
     </row>
     <row r="29" spans="2:4" ht="93.75" customHeight="1">
-      <c r="B29" s="59" t="s">
+      <c r="B29" s="63" t="s">
         <v>86</v>
       </c>
       <c r="C29" s="57"/>
@@ -3723,21 +3719,21 @@
       <c r="D34" s="37"/>
     </row>
     <row r="37" spans="2:4" ht="12.75">
-      <c r="B37" s="56" t="s">
+      <c r="B37" s="62" t="s">
         <v>89</v>
       </c>
       <c r="C37" s="57"/>
       <c r="D37" s="58"/>
     </row>
     <row r="38" spans="2:4" ht="12.75">
-      <c r="B38" s="56" t="s">
+      <c r="B38" s="62" t="s">
         <v>2</v>
       </c>
       <c r="C38" s="57"/>
       <c r="D38" s="58"/>
     </row>
     <row r="39" spans="2:4" ht="226.5" customHeight="1">
-      <c r="B39" s="59" t="s">
+      <c r="B39" s="63" t="s">
         <v>90</v>
       </c>
       <c r="C39" s="57"/>

--- a/Proyecto/docs/Pruebas de Caja Negra_Blanca/Pruebas de Caja Blanca-SistemaPOS.xlsx
+++ b/Proyecto/docs/Pruebas de Caja Negra_Blanca/Pruebas de Caja Blanca-SistemaPOS.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29929"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30026"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/01f32f4e8c9e178e/Desktop/Analisis y Diseño/36289_AnalisisYDisenoDeSistemas/Proyecto/docs/Pruebas de Caja Negra_Blanca/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://uabcedumx-my.sharepoint.com/personal/joshua_osorio_uabc_edu_mx/Documents/8_Semestre/36289_AnalisisYDisenoDeSistemas/Proyecto/docs/Pruebas de Caja Negra_Blanca/"/>
     </mc:Choice>
   </mc:AlternateContent>
   <xr:revisionPtr revIDLastSave="268" documentId="11_94B3DA253D63A0DE445D4A83045116E5BA157345" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{F93F91EE-E161-44B5-A001-4D3034166A34}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="4" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Usuario - Administrador" sheetId="1" r:id="rId1"/>
@@ -1489,27 +1489,27 @@
     </xf>
     <xf numFmtId="0" fontId="22" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="18" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="6" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="5" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="3" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="2" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="3" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="17" fillId="3" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="21" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="17" fillId="3" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="3" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="5" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="2" fillId="3" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="2" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
@@ -1532,10 +1532,6 @@
     </ext>
   </extLst>
 </styleSheet>
-</file>
-
-<file path=xl/persons/person.xml><?xml version="1.0" encoding="utf-8"?>
-<personList xmlns="http://schemas.microsoft.com/office/spreadsheetml/2018/threadedcomments" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main"/>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -1748,11 +1744,11 @@
   </cols>
   <sheetData>
     <row r="2" spans="2:4">
-      <c r="B2" s="60" t="s">
+      <c r="B2" s="63" t="s">
         <v>0</v>
       </c>
-      <c r="C2" s="61"/>
-      <c r="D2" s="61"/>
+      <c r="C2" s="64"/>
+      <c r="D2" s="64"/>
     </row>
     <row r="3" spans="2:4" ht="12.75">
       <c r="B3" s="1"/>
@@ -1763,22 +1759,22 @@
       <c r="B4" s="62" t="s">
         <v>1</v>
       </c>
-      <c r="C4" s="57"/>
-      <c r="D4" s="58"/>
+      <c r="C4" s="60"/>
+      <c r="D4" s="61"/>
     </row>
     <row r="5" spans="2:4" ht="12.75">
       <c r="B5" s="62" t="s">
         <v>2</v>
       </c>
-      <c r="C5" s="57"/>
-      <c r="D5" s="58"/>
+      <c r="C5" s="60"/>
+      <c r="D5" s="61"/>
     </row>
     <row r="6" spans="2:4" ht="192" customHeight="1">
-      <c r="B6" s="63" t="s">
+      <c r="B6" s="66" t="s">
         <v>3</v>
       </c>
-      <c r="C6" s="57"/>
-      <c r="D6" s="58"/>
+      <c r="C6" s="60"/>
+      <c r="D6" s="61"/>
     </row>
     <row r="7" spans="2:4" ht="12.75">
       <c r="B7" s="2" t="s">
@@ -1836,25 +1832,25 @@
       </c>
     </row>
     <row r="15" spans="2:4" ht="12.75">
-      <c r="B15" s="56" t="s">
+      <c r="B15" s="67" t="s">
         <v>13</v>
       </c>
-      <c r="C15" s="57"/>
-      <c r="D15" s="58"/>
+      <c r="C15" s="60"/>
+      <c r="D15" s="61"/>
     </row>
     <row r="16" spans="2:4" ht="22.5" customHeight="1">
-      <c r="B16" s="56" t="s">
-        <v>2</v>
-      </c>
-      <c r="C16" s="57"/>
-      <c r="D16" s="58"/>
+      <c r="B16" s="67" t="s">
+        <v>2</v>
+      </c>
+      <c r="C16" s="60"/>
+      <c r="D16" s="61"/>
     </row>
     <row r="17" spans="2:4" ht="177" customHeight="1">
-      <c r="B17" s="59" t="s">
+      <c r="B17" s="68" t="s">
         <v>14</v>
       </c>
-      <c r="C17" s="57"/>
-      <c r="D17" s="58"/>
+      <c r="C17" s="60"/>
+      <c r="D17" s="61"/>
     </row>
     <row r="18" spans="2:4" ht="14.25" customHeight="1">
       <c r="B18" s="8" t="s">
@@ -1901,25 +1897,25 @@
       </c>
     </row>
     <row r="25" spans="2:4" ht="12.75">
-      <c r="B25" s="56" t="s">
+      <c r="B25" s="67" t="s">
         <v>18</v>
       </c>
-      <c r="C25" s="57"/>
-      <c r="D25" s="58"/>
+      <c r="C25" s="60"/>
+      <c r="D25" s="61"/>
     </row>
     <row r="26" spans="2:4" ht="12.75">
-      <c r="B26" s="56" t="s">
-        <v>2</v>
-      </c>
-      <c r="C26" s="57"/>
-      <c r="D26" s="58"/>
+      <c r="B26" s="67" t="s">
+        <v>2</v>
+      </c>
+      <c r="C26" s="60"/>
+      <c r="D26" s="61"/>
     </row>
     <row r="27" spans="2:4" ht="213" customHeight="1">
-      <c r="B27" s="59" t="s">
+      <c r="B27" s="68" t="s">
         <v>19</v>
       </c>
-      <c r="C27" s="57"/>
-      <c r="D27" s="58"/>
+      <c r="C27" s="60"/>
+      <c r="D27" s="61"/>
     </row>
     <row r="28" spans="2:4" ht="12.75">
       <c r="B28" s="10" t="s">
@@ -1977,25 +1973,25 @@
       </c>
     </row>
     <row r="34" spans="2:4" ht="12.75">
-      <c r="B34" s="56" t="s">
+      <c r="B34" s="67" t="s">
         <v>24</v>
       </c>
-      <c r="C34" s="57"/>
-      <c r="D34" s="58"/>
+      <c r="C34" s="60"/>
+      <c r="D34" s="61"/>
     </row>
     <row r="35" spans="2:4" ht="12.75">
-      <c r="B35" s="56" t="s">
-        <v>2</v>
-      </c>
-      <c r="C35" s="57"/>
-      <c r="D35" s="58"/>
+      <c r="B35" s="67" t="s">
+        <v>2</v>
+      </c>
+      <c r="C35" s="60"/>
+      <c r="D35" s="61"/>
     </row>
     <row r="36" spans="2:4" ht="144" customHeight="1">
-      <c r="B36" s="59" t="s">
+      <c r="B36" s="68" t="s">
         <v>25</v>
       </c>
-      <c r="C36" s="57"/>
-      <c r="D36" s="58"/>
+      <c r="C36" s="60"/>
+      <c r="D36" s="61"/>
     </row>
     <row r="37" spans="2:4" ht="12.75">
       <c r="B37" s="10" t="s">
@@ -2042,25 +2038,25 @@
       </c>
     </row>
     <row r="43" spans="2:4" ht="12.75">
-      <c r="B43" s="56" t="s">
+      <c r="B43" s="67" t="s">
         <v>28</v>
       </c>
-      <c r="C43" s="57"/>
-      <c r="D43" s="58"/>
+      <c r="C43" s="60"/>
+      <c r="D43" s="61"/>
     </row>
     <row r="44" spans="2:4" ht="12.75">
-      <c r="B44" s="56" t="s">
-        <v>2</v>
-      </c>
-      <c r="C44" s="57"/>
-      <c r="D44" s="58"/>
+      <c r="B44" s="67" t="s">
+        <v>2</v>
+      </c>
+      <c r="C44" s="60"/>
+      <c r="D44" s="61"/>
     </row>
     <row r="45" spans="2:4" ht="150" customHeight="1">
-      <c r="B45" s="59" t="s">
+      <c r="B45" s="68" t="s">
         <v>29</v>
       </c>
-      <c r="C45" s="57"/>
-      <c r="D45" s="58"/>
+      <c r="C45" s="60"/>
+      <c r="D45" s="61"/>
     </row>
     <row r="46" spans="2:4" ht="12.75">
       <c r="B46" s="10" t="s">
@@ -2107,25 +2103,25 @@
       </c>
     </row>
     <row r="52" spans="2:4" ht="12.75">
-      <c r="B52" s="56" t="s">
+      <c r="B52" s="67" t="s">
         <v>33</v>
       </c>
-      <c r="C52" s="57"/>
-      <c r="D52" s="58"/>
+      <c r="C52" s="60"/>
+      <c r="D52" s="61"/>
     </row>
     <row r="53" spans="2:4" ht="12.75">
-      <c r="B53" s="56" t="s">
-        <v>2</v>
-      </c>
-      <c r="C53" s="57"/>
-      <c r="D53" s="58"/>
+      <c r="B53" s="67" t="s">
+        <v>2</v>
+      </c>
+      <c r="C53" s="60"/>
+      <c r="D53" s="61"/>
     </row>
     <row r="54" spans="2:4" ht="99" customHeight="1">
-      <c r="B54" s="59" t="s">
+      <c r="B54" s="68" t="s">
         <v>34</v>
       </c>
-      <c r="C54" s="57"/>
-      <c r="D54" s="58"/>
+      <c r="C54" s="60"/>
+      <c r="D54" s="61"/>
     </row>
     <row r="55" spans="2:4" ht="12.75">
       <c r="B55" s="19" t="s">
@@ -2172,25 +2168,25 @@
       </c>
     </row>
     <row r="61" spans="2:4" ht="12.75">
-      <c r="B61" s="56" t="s">
+      <c r="B61" s="67" t="s">
         <v>37</v>
       </c>
-      <c r="C61" s="57"/>
-      <c r="D61" s="58"/>
+      <c r="C61" s="60"/>
+      <c r="D61" s="61"/>
     </row>
     <row r="62" spans="2:4" ht="12.75">
-      <c r="B62" s="56" t="s">
-        <v>2</v>
-      </c>
-      <c r="C62" s="57"/>
-      <c r="D62" s="58"/>
+      <c r="B62" s="67" t="s">
+        <v>2</v>
+      </c>
+      <c r="C62" s="60"/>
+      <c r="D62" s="61"/>
     </row>
     <row r="63" spans="2:4" ht="227.25" customHeight="1">
-      <c r="B63" s="59" t="s">
+      <c r="B63" s="68" t="s">
         <v>38</v>
       </c>
-      <c r="C63" s="57"/>
-      <c r="D63" s="58"/>
+      <c r="C63" s="60"/>
+      <c r="D63" s="61"/>
     </row>
     <row r="64" spans="2:4" ht="12.75">
       <c r="B64" s="23" t="s">
@@ -2248,25 +2244,25 @@
       </c>
     </row>
     <row r="71" spans="2:4" ht="12.75">
-      <c r="B71" s="56" t="s">
+      <c r="B71" s="67" t="s">
         <v>43</v>
       </c>
-      <c r="C71" s="57"/>
-      <c r="D71" s="58"/>
+      <c r="C71" s="60"/>
+      <c r="D71" s="61"/>
     </row>
     <row r="72" spans="2:4" ht="12.75">
-      <c r="B72" s="56" t="s">
-        <v>2</v>
-      </c>
-      <c r="C72" s="57"/>
-      <c r="D72" s="58"/>
+      <c r="B72" s="67" t="s">
+        <v>2</v>
+      </c>
+      <c r="C72" s="60"/>
+      <c r="D72" s="61"/>
     </row>
     <row r="73" spans="2:4" ht="96" customHeight="1">
-      <c r="B73" s="59" t="s">
+      <c r="B73" s="68" t="s">
         <v>44</v>
       </c>
-      <c r="C73" s="57"/>
-      <c r="D73" s="58"/>
+      <c r="C73" s="60"/>
+      <c r="D73" s="61"/>
     </row>
     <row r="74" spans="2:4" ht="12.75">
       <c r="B74" s="26" t="s">
@@ -2314,21 +2310,6 @@
     </row>
   </sheetData>
   <mergeCells count="25">
-    <mergeCell ref="B2:D2"/>
-    <mergeCell ref="B4:D4"/>
-    <mergeCell ref="B5:D5"/>
-    <mergeCell ref="B6:D6"/>
-    <mergeCell ref="B15:D15"/>
-    <mergeCell ref="B16:D16"/>
-    <mergeCell ref="B17:D17"/>
-    <mergeCell ref="B25:D25"/>
-    <mergeCell ref="B26:D26"/>
-    <mergeCell ref="B27:D27"/>
-    <mergeCell ref="B34:D34"/>
-    <mergeCell ref="B35:D35"/>
-    <mergeCell ref="B36:D36"/>
-    <mergeCell ref="B43:D43"/>
-    <mergeCell ref="B63:D63"/>
     <mergeCell ref="B71:D71"/>
     <mergeCell ref="B72:D72"/>
     <mergeCell ref="B73:D73"/>
@@ -2339,6 +2320,21 @@
     <mergeCell ref="B54:D54"/>
     <mergeCell ref="B61:D61"/>
     <mergeCell ref="B62:D62"/>
+    <mergeCell ref="B34:D34"/>
+    <mergeCell ref="B35:D35"/>
+    <mergeCell ref="B36:D36"/>
+    <mergeCell ref="B43:D43"/>
+    <mergeCell ref="B63:D63"/>
+    <mergeCell ref="B16:D16"/>
+    <mergeCell ref="B17:D17"/>
+    <mergeCell ref="B25:D25"/>
+    <mergeCell ref="B26:D26"/>
+    <mergeCell ref="B27:D27"/>
+    <mergeCell ref="B2:D2"/>
+    <mergeCell ref="B4:D4"/>
+    <mergeCell ref="B5:D5"/>
+    <mergeCell ref="B6:D6"/>
+    <mergeCell ref="B15:D15"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
@@ -2359,11 +2355,11 @@
   </cols>
   <sheetData>
     <row r="2" spans="2:4">
-      <c r="B2" s="60" t="s">
+      <c r="B2" s="63" t="s">
         <v>47</v>
       </c>
-      <c r="C2" s="61"/>
-      <c r="D2" s="61"/>
+      <c r="C2" s="64"/>
+      <c r="D2" s="64"/>
     </row>
     <row r="3" spans="2:4" ht="12.75">
       <c r="B3" s="1"/>
@@ -2374,22 +2370,22 @@
       <c r="B4" s="62" t="s">
         <v>1</v>
       </c>
-      <c r="C4" s="57"/>
-      <c r="D4" s="58"/>
+      <c r="C4" s="60"/>
+      <c r="D4" s="61"/>
     </row>
     <row r="5" spans="2:4" ht="12.75">
       <c r="B5" s="62" t="s">
         <v>2</v>
       </c>
-      <c r="C5" s="57"/>
-      <c r="D5" s="58"/>
+      <c r="C5" s="60"/>
+      <c r="D5" s="61"/>
     </row>
     <row r="6" spans="2:4" ht="184.5" customHeight="1">
-      <c r="B6" s="63" t="s">
+      <c r="B6" s="66" t="s">
         <v>3</v>
       </c>
-      <c r="C6" s="57"/>
-      <c r="D6" s="58"/>
+      <c r="C6" s="60"/>
+      <c r="D6" s="61"/>
     </row>
     <row r="7" spans="2:4" ht="12.75">
       <c r="B7" s="2" t="s">
@@ -2450,22 +2446,22 @@
       <c r="B15" s="62" t="s">
         <v>48</v>
       </c>
-      <c r="C15" s="57"/>
-      <c r="D15" s="58"/>
+      <c r="C15" s="60"/>
+      <c r="D15" s="61"/>
     </row>
     <row r="16" spans="2:4" ht="12.75">
       <c r="B16" s="62" t="s">
         <v>2</v>
       </c>
-      <c r="C16" s="57"/>
-      <c r="D16" s="58"/>
+      <c r="C16" s="60"/>
+      <c r="D16" s="61"/>
     </row>
     <row r="17" spans="2:4" ht="222.75" customHeight="1">
-      <c r="B17" s="63" t="s">
+      <c r="B17" s="66" t="s">
         <v>49</v>
       </c>
-      <c r="C17" s="57"/>
-      <c r="D17" s="58"/>
+      <c r="C17" s="60"/>
+      <c r="D17" s="61"/>
     </row>
     <row r="18" spans="2:4" ht="12.75">
       <c r="B18" s="26" t="s">
@@ -2526,22 +2522,22 @@
       <c r="B26" s="62" t="s">
         <v>54</v>
       </c>
-      <c r="C26" s="57"/>
-      <c r="D26" s="58"/>
+      <c r="C26" s="60"/>
+      <c r="D26" s="61"/>
     </row>
     <row r="27" spans="2:4" ht="12.75">
       <c r="B27" s="62" t="s">
         <v>2</v>
       </c>
-      <c r="C27" s="57"/>
-      <c r="D27" s="58"/>
+      <c r="C27" s="60"/>
+      <c r="D27" s="61"/>
     </row>
     <row r="28" spans="2:4" ht="138" customHeight="1">
-      <c r="B28" s="63" t="s">
+      <c r="B28" s="66" t="s">
         <v>55</v>
       </c>
-      <c r="C28" s="57"/>
-      <c r="D28" s="58"/>
+      <c r="C28" s="60"/>
+      <c r="D28" s="61"/>
     </row>
     <row r="29" spans="2:4" ht="12.75">
       <c r="B29" s="26" t="s">
@@ -2596,22 +2592,22 @@
       <c r="B36" s="62" t="s">
         <v>59</v>
       </c>
-      <c r="C36" s="57"/>
-      <c r="D36" s="58"/>
+      <c r="C36" s="60"/>
+      <c r="D36" s="61"/>
     </row>
     <row r="37" spans="2:4" ht="16.5" customHeight="1">
       <c r="B37" s="62" t="s">
         <v>2</v>
       </c>
-      <c r="C37" s="57"/>
-      <c r="D37" s="58"/>
+      <c r="C37" s="60"/>
+      <c r="D37" s="61"/>
     </row>
     <row r="38" spans="2:4" ht="212.25" customHeight="1">
-      <c r="B38" s="63" t="s">
+      <c r="B38" s="66" t="s">
         <v>60</v>
       </c>
-      <c r="C38" s="57"/>
-      <c r="D38" s="58"/>
+      <c r="C38" s="60"/>
+      <c r="D38" s="61"/>
     </row>
     <row r="39" spans="2:4" ht="12.75">
       <c r="B39" s="26" t="s">
@@ -2661,22 +2657,22 @@
       <c r="B46" s="62" t="s">
         <v>64</v>
       </c>
-      <c r="C46" s="57"/>
-      <c r="D46" s="58"/>
+      <c r="C46" s="60"/>
+      <c r="D46" s="61"/>
     </row>
     <row r="47" spans="2:4" ht="12.75">
       <c r="B47" s="62" t="s">
         <v>2</v>
       </c>
-      <c r="C47" s="57"/>
-      <c r="D47" s="58"/>
+      <c r="C47" s="60"/>
+      <c r="D47" s="61"/>
     </row>
     <row r="48" spans="2:4" ht="139.5" customHeight="1">
-      <c r="B48" s="63" t="s">
+      <c r="B48" s="66" t="s">
         <v>65</v>
       </c>
-      <c r="C48" s="57"/>
-      <c r="D48" s="58"/>
+      <c r="C48" s="60"/>
+      <c r="D48" s="61"/>
     </row>
     <row r="49" spans="2:4" ht="12.75">
       <c r="B49" s="26" t="s">
@@ -2726,22 +2722,22 @@
       <c r="B56" s="62" t="s">
         <v>69</v>
       </c>
-      <c r="C56" s="57"/>
-      <c r="D56" s="58"/>
+      <c r="C56" s="60"/>
+      <c r="D56" s="61"/>
     </row>
     <row r="57" spans="2:4" ht="12.75">
       <c r="B57" s="62" t="s">
         <v>2</v>
       </c>
-      <c r="C57" s="57"/>
-      <c r="D57" s="58"/>
+      <c r="C57" s="60"/>
+      <c r="D57" s="61"/>
     </row>
     <row r="58" spans="2:4" ht="193.5" customHeight="1">
-      <c r="B58" s="63" t="s">
+      <c r="B58" s="66" t="s">
         <v>70</v>
       </c>
-      <c r="C58" s="57"/>
-      <c r="D58" s="58"/>
+      <c r="C58" s="60"/>
+      <c r="D58" s="61"/>
     </row>
     <row r="59" spans="2:4" ht="12.75">
       <c r="B59" s="26" t="s">
@@ -2789,16 +2785,6 @@
     </row>
   </sheetData>
   <mergeCells count="19">
-    <mergeCell ref="B2:D2"/>
-    <mergeCell ref="B4:D4"/>
-    <mergeCell ref="B5:D5"/>
-    <mergeCell ref="B6:D6"/>
-    <mergeCell ref="B15:D15"/>
-    <mergeCell ref="B16:D16"/>
-    <mergeCell ref="B17:D17"/>
-    <mergeCell ref="B47:D47"/>
-    <mergeCell ref="B48:D48"/>
-    <mergeCell ref="B56:D56"/>
     <mergeCell ref="B57:D57"/>
     <mergeCell ref="B58:D58"/>
     <mergeCell ref="B26:D26"/>
@@ -2808,6 +2794,16 @@
     <mergeCell ref="B37:D37"/>
     <mergeCell ref="B38:D38"/>
     <mergeCell ref="B46:D46"/>
+    <mergeCell ref="B16:D16"/>
+    <mergeCell ref="B17:D17"/>
+    <mergeCell ref="B47:D47"/>
+    <mergeCell ref="B48:D48"/>
+    <mergeCell ref="B56:D56"/>
+    <mergeCell ref="B2:D2"/>
+    <mergeCell ref="B4:D4"/>
+    <mergeCell ref="B5:D5"/>
+    <mergeCell ref="B6:D6"/>
+    <mergeCell ref="B15:D15"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
@@ -2824,11 +2820,11 @@
   </cols>
   <sheetData>
     <row r="3" spans="2:4" ht="15.75">
-      <c r="B3" s="60" t="s">
+      <c r="B3" s="63" t="s">
         <v>135</v>
       </c>
-      <c r="C3" s="61"/>
-      <c r="D3" s="61"/>
+      <c r="C3" s="64"/>
+      <c r="D3" s="64"/>
     </row>
     <row r="4" spans="2:4">
       <c r="B4" s="1"/>
@@ -2839,22 +2835,22 @@
       <c r="B5" s="62" t="s">
         <v>111</v>
       </c>
-      <c r="C5" s="57"/>
-      <c r="D5" s="58"/>
+      <c r="C5" s="60"/>
+      <c r="D5" s="61"/>
     </row>
     <row r="6" spans="2:4" ht="15.75" customHeight="1">
       <c r="B6" s="62" t="s">
         <v>2</v>
       </c>
-      <c r="C6" s="57"/>
-      <c r="D6" s="58"/>
+      <c r="C6" s="60"/>
+      <c r="D6" s="61"/>
     </row>
     <row r="7" spans="2:4" ht="288.75" customHeight="1">
-      <c r="B7" s="64" t="s">
+      <c r="B7" s="65" t="s">
         <v>112</v>
       </c>
-      <c r="C7" s="65"/>
-      <c r="D7" s="66"/>
+      <c r="C7" s="57"/>
+      <c r="D7" s="58"/>
     </row>
     <row r="8" spans="2:4">
       <c r="B8" s="43" t="s">
@@ -2912,25 +2908,25 @@
       </c>
     </row>
     <row r="16" spans="2:4">
-      <c r="B16" s="67" t="s">
+      <c r="B16" s="59" t="s">
         <v>121</v>
       </c>
-      <c r="C16" s="57"/>
-      <c r="D16" s="58"/>
+      <c r="C16" s="60"/>
+      <c r="D16" s="61"/>
     </row>
     <row r="17" spans="2:4" ht="18.75" customHeight="1">
       <c r="B17" s="62" t="s">
         <v>2</v>
       </c>
-      <c r="C17" s="57"/>
-      <c r="D17" s="58"/>
+      <c r="C17" s="60"/>
+      <c r="D17" s="61"/>
     </row>
     <row r="18" spans="2:4" ht="132" customHeight="1">
-      <c r="B18" s="68" t="s">
+      <c r="B18" s="56" t="s">
         <v>117</v>
       </c>
-      <c r="C18" s="65"/>
-      <c r="D18" s="66"/>
+      <c r="C18" s="57"/>
+      <c r="D18" s="58"/>
     </row>
     <row r="19" spans="2:4">
       <c r="B19" s="43" t="s">
@@ -2982,25 +2978,25 @@
       <c r="D23" s="53"/>
     </row>
     <row r="25" spans="2:4">
-      <c r="B25" s="67" t="s">
+      <c r="B25" s="59" t="s">
         <v>126</v>
       </c>
-      <c r="C25" s="57"/>
-      <c r="D25" s="58"/>
+      <c r="C25" s="60"/>
+      <c r="D25" s="61"/>
     </row>
     <row r="26" spans="2:4" ht="13.5" customHeight="1">
       <c r="B26" s="62" t="s">
         <v>2</v>
       </c>
-      <c r="C26" s="57"/>
-      <c r="D26" s="58"/>
+      <c r="C26" s="60"/>
+      <c r="D26" s="61"/>
     </row>
     <row r="27" spans="2:4" ht="168" customHeight="1">
-      <c r="B27" s="68" t="s">
+      <c r="B27" s="56" t="s">
         <v>125</v>
       </c>
-      <c r="C27" s="65"/>
-      <c r="D27" s="66"/>
+      <c r="C27" s="57"/>
+      <c r="D27" s="58"/>
     </row>
     <row r="28" spans="2:4">
       <c r="B28" s="43" t="s">
@@ -3047,25 +3043,25 @@
       </c>
     </row>
     <row r="34" spans="2:4">
-      <c r="B34" s="67" t="s">
+      <c r="B34" s="59" t="s">
         <v>130</v>
       </c>
-      <c r="C34" s="57"/>
-      <c r="D34" s="58"/>
+      <c r="C34" s="60"/>
+      <c r="D34" s="61"/>
     </row>
     <row r="35" spans="2:4">
       <c r="B35" s="62" t="s">
         <v>2</v>
       </c>
-      <c r="C35" s="57"/>
-      <c r="D35" s="58"/>
+      <c r="C35" s="60"/>
+      <c r="D35" s="61"/>
     </row>
     <row r="36" spans="2:4" ht="185.25" customHeight="1">
-      <c r="B36" s="68" t="s">
+      <c r="B36" s="56" t="s">
         <v>127</v>
       </c>
-      <c r="C36" s="65"/>
-      <c r="D36" s="66"/>
+      <c r="C36" s="57"/>
+      <c r="D36" s="58"/>
     </row>
     <row r="37" spans="2:4">
       <c r="B37" s="43" t="s">
@@ -3112,25 +3108,25 @@
       </c>
     </row>
     <row r="43" spans="2:4">
-      <c r="B43" s="67" t="s">
+      <c r="B43" s="59" t="s">
         <v>111</v>
       </c>
-      <c r="C43" s="57"/>
-      <c r="D43" s="58"/>
+      <c r="C43" s="60"/>
+      <c r="D43" s="61"/>
     </row>
     <row r="44" spans="2:4">
       <c r="B44" s="62" t="s">
         <v>2</v>
       </c>
-      <c r="C44" s="57"/>
-      <c r="D44" s="58"/>
+      <c r="C44" s="60"/>
+      <c r="D44" s="61"/>
     </row>
     <row r="45" spans="2:4" ht="222.75" customHeight="1">
-      <c r="B45" s="68" t="s">
+      <c r="B45" s="56" t="s">
         <v>131</v>
       </c>
-      <c r="C45" s="65"/>
-      <c r="D45" s="66"/>
+      <c r="C45" s="57"/>
+      <c r="D45" s="58"/>
     </row>
     <row r="46" spans="2:4">
       <c r="B46" s="43" t="s">
@@ -3189,6 +3185,12 @@
     </row>
   </sheetData>
   <mergeCells count="16">
+    <mergeCell ref="B17:D17"/>
+    <mergeCell ref="B3:D3"/>
+    <mergeCell ref="B5:D5"/>
+    <mergeCell ref="B6:D6"/>
+    <mergeCell ref="B7:D7"/>
+    <mergeCell ref="B16:D16"/>
     <mergeCell ref="B36:D36"/>
     <mergeCell ref="B43:D43"/>
     <mergeCell ref="B44:D44"/>
@@ -3199,12 +3201,6 @@
     <mergeCell ref="B27:D27"/>
     <mergeCell ref="B34:D34"/>
     <mergeCell ref="B35:D35"/>
-    <mergeCell ref="B17:D17"/>
-    <mergeCell ref="B3:D3"/>
-    <mergeCell ref="B5:D5"/>
-    <mergeCell ref="B6:D6"/>
-    <mergeCell ref="B7:D7"/>
-    <mergeCell ref="B16:D16"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
@@ -3221,11 +3217,11 @@
   </cols>
   <sheetData>
     <row r="4" spans="2:4" ht="15.75">
-      <c r="B4" s="60" t="s">
+      <c r="B4" s="63" t="s">
         <v>94</v>
       </c>
-      <c r="C4" s="61"/>
-      <c r="D4" s="61"/>
+      <c r="C4" s="64"/>
+      <c r="D4" s="64"/>
     </row>
     <row r="5" spans="2:4">
       <c r="B5" s="1"/>
@@ -3236,22 +3232,22 @@
       <c r="B6" s="62" t="s">
         <v>95</v>
       </c>
-      <c r="C6" s="57"/>
-      <c r="D6" s="58"/>
+      <c r="C6" s="60"/>
+      <c r="D6" s="61"/>
     </row>
     <row r="7" spans="2:4">
       <c r="B7" s="62" t="s">
         <v>2</v>
       </c>
-      <c r="C7" s="57"/>
-      <c r="D7" s="58"/>
+      <c r="C7" s="60"/>
+      <c r="D7" s="61"/>
     </row>
     <row r="8" spans="2:4" ht="249" customHeight="1">
-      <c r="B8" s="64" t="s">
+      <c r="B8" s="65" t="s">
         <v>96</v>
       </c>
-      <c r="C8" s="65"/>
-      <c r="D8" s="66"/>
+      <c r="C8" s="57"/>
+      <c r="D8" s="58"/>
     </row>
     <row r="9" spans="2:4">
       <c r="B9" s="43" t="s">
@@ -3309,25 +3305,25 @@
       </c>
     </row>
     <row r="16" spans="2:4">
-      <c r="B16" s="67" t="s">
+      <c r="B16" s="59" t="s">
         <v>101</v>
       </c>
-      <c r="C16" s="57"/>
-      <c r="D16" s="58"/>
+      <c r="C16" s="60"/>
+      <c r="D16" s="61"/>
     </row>
     <row r="17" spans="2:4">
       <c r="B17" s="62" t="s">
         <v>2</v>
       </c>
-      <c r="C17" s="57"/>
-      <c r="D17" s="58"/>
+      <c r="C17" s="60"/>
+      <c r="D17" s="61"/>
     </row>
     <row r="18" spans="2:4" ht="248.25" customHeight="1">
-      <c r="B18" s="68" t="s">
+      <c r="B18" s="56" t="s">
         <v>102</v>
       </c>
-      <c r="C18" s="65"/>
-      <c r="D18" s="66"/>
+      <c r="C18" s="57"/>
+      <c r="D18" s="58"/>
     </row>
     <row r="19" spans="2:4">
       <c r="B19" s="43" t="s">
@@ -3379,18 +3375,18 @@
       <c r="D23" s="46"/>
     </row>
     <row r="26" spans="2:4">
-      <c r="B26" s="67" t="s">
+      <c r="B26" s="59" t="s">
         <v>106</v>
       </c>
-      <c r="C26" s="57"/>
-      <c r="D26" s="58"/>
+      <c r="C26" s="60"/>
+      <c r="D26" s="61"/>
     </row>
     <row r="27" spans="2:4">
       <c r="B27" s="69" t="s">
         <v>2</v>
       </c>
-      <c r="C27" s="65"/>
-      <c r="D27" s="66"/>
+      <c r="C27" s="57"/>
+      <c r="D27" s="58"/>
     </row>
     <row r="28" spans="2:4" ht="246" customHeight="1">
       <c r="B28" s="70" t="s">
@@ -3456,16 +3452,16 @@
     </row>
   </sheetData>
   <mergeCells count="10">
+    <mergeCell ref="B17:D17"/>
+    <mergeCell ref="B18:D18"/>
+    <mergeCell ref="B26:D26"/>
+    <mergeCell ref="B27:D27"/>
+    <mergeCell ref="B28:D28"/>
     <mergeCell ref="B4:D4"/>
     <mergeCell ref="B6:D6"/>
     <mergeCell ref="B7:D7"/>
     <mergeCell ref="B8:D8"/>
     <mergeCell ref="B16:D16"/>
-    <mergeCell ref="B17:D17"/>
-    <mergeCell ref="B18:D18"/>
-    <mergeCell ref="B26:D26"/>
-    <mergeCell ref="B27:D27"/>
-    <mergeCell ref="B28:D28"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
@@ -3485,11 +3481,11 @@
   </cols>
   <sheetData>
     <row r="3" spans="2:4">
-      <c r="B3" s="60" t="s">
+      <c r="B3" s="63" t="s">
         <v>74</v>
       </c>
-      <c r="C3" s="61"/>
-      <c r="D3" s="61"/>
+      <c r="C3" s="64"/>
+      <c r="D3" s="64"/>
     </row>
     <row r="4" spans="2:4" ht="12.75">
       <c r="B4" s="1"/>
@@ -3500,22 +3496,22 @@
       <c r="B5" s="62" t="s">
         <v>75</v>
       </c>
-      <c r="C5" s="57"/>
-      <c r="D5" s="58"/>
+      <c r="C5" s="60"/>
+      <c r="D5" s="61"/>
     </row>
     <row r="6" spans="2:4" ht="12.75">
       <c r="B6" s="62" t="s">
         <v>2</v>
       </c>
-      <c r="C6" s="57"/>
-      <c r="D6" s="58"/>
+      <c r="C6" s="60"/>
+      <c r="D6" s="61"/>
     </row>
     <row r="7" spans="2:4" ht="229.5" customHeight="1">
-      <c r="B7" s="63" t="s">
+      <c r="B7" s="66" t="s">
         <v>76</v>
       </c>
-      <c r="C7" s="57"/>
-      <c r="D7" s="58"/>
+      <c r="C7" s="60"/>
+      <c r="D7" s="61"/>
     </row>
     <row r="8" spans="2:4" ht="12.75">
       <c r="B8" s="26" t="s">
@@ -3576,22 +3572,22 @@
       <c r="B16" s="62" t="s">
         <v>80</v>
       </c>
-      <c r="C16" s="57"/>
-      <c r="D16" s="58"/>
+      <c r="C16" s="60"/>
+      <c r="D16" s="61"/>
     </row>
     <row r="17" spans="2:4" ht="12.75">
       <c r="B17" s="62" t="s">
         <v>2</v>
       </c>
-      <c r="C17" s="57"/>
-      <c r="D17" s="58"/>
+      <c r="C17" s="60"/>
+      <c r="D17" s="61"/>
     </row>
     <row r="18" spans="2:4" ht="174" customHeight="1">
-      <c r="B18" s="63" t="s">
+      <c r="B18" s="66" t="s">
         <v>81</v>
       </c>
-      <c r="C18" s="57"/>
-      <c r="D18" s="58"/>
+      <c r="C18" s="60"/>
+      <c r="D18" s="61"/>
     </row>
     <row r="19" spans="2:4" ht="12.75">
       <c r="B19" s="26" t="s">
@@ -3652,22 +3648,22 @@
       <c r="B27" s="62" t="s">
         <v>85</v>
       </c>
-      <c r="C27" s="57"/>
-      <c r="D27" s="58"/>
+      <c r="C27" s="60"/>
+      <c r="D27" s="61"/>
     </row>
     <row r="28" spans="2:4" ht="12.75">
       <c r="B28" s="62" t="s">
         <v>2</v>
       </c>
-      <c r="C28" s="57"/>
-      <c r="D28" s="58"/>
+      <c r="C28" s="60"/>
+      <c r="D28" s="61"/>
     </row>
     <row r="29" spans="2:4" ht="93.75" customHeight="1">
-      <c r="B29" s="63" t="s">
+      <c r="B29" s="66" t="s">
         <v>86</v>
       </c>
-      <c r="C29" s="57"/>
-      <c r="D29" s="58"/>
+      <c r="C29" s="60"/>
+      <c r="D29" s="61"/>
     </row>
     <row r="30" spans="2:4" ht="12.75">
       <c r="B30" s="33" t="s">
@@ -3722,22 +3718,22 @@
       <c r="B37" s="62" t="s">
         <v>89</v>
       </c>
-      <c r="C37" s="57"/>
-      <c r="D37" s="58"/>
+      <c r="C37" s="60"/>
+      <c r="D37" s="61"/>
     </row>
     <row r="38" spans="2:4" ht="12.75">
       <c r="B38" s="62" t="s">
         <v>2</v>
       </c>
-      <c r="C38" s="57"/>
-      <c r="D38" s="58"/>
+      <c r="C38" s="60"/>
+      <c r="D38" s="61"/>
     </row>
     <row r="39" spans="2:4" ht="226.5" customHeight="1">
-      <c r="B39" s="63" t="s">
+      <c r="B39" s="66" t="s">
         <v>90</v>
       </c>
-      <c r="C39" s="57"/>
-      <c r="D39" s="58"/>
+      <c r="C39" s="60"/>
+      <c r="D39" s="61"/>
     </row>
     <row r="40" spans="2:4" ht="12.75">
       <c r="B40" s="26" t="s">
